--- a/Indicator_4/Real_data/Swordfish_NAtl.xlsx
+++ b/Indicator_4/Real_data/Swordfish_NAtl.xlsx
@@ -1,22 +1,300 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\EcoTest_Train\Indicator_4\Real_data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C82BE9E0-4D0D-4B73-AA24-C4E9DA65F655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
     <sheet name="Time_series" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="89">
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Swordfish_NAtl</t>
+  </si>
+  <si>
+    <t>E.g. 'Swordfish_Natl'</t>
+  </si>
+  <si>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>max_age</t>
+  </si>
+  <si>
+    <t>14.979</t>
+  </si>
+  <si>
+    <t>Age to 5% natural survival</t>
+  </si>
+  <si>
+    <t>Life history</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>0.093</t>
+  </si>
+  <si>
+    <t>von Bertalannfy K</t>
+  </si>
+  <si>
+    <t>Linf</t>
+  </si>
+  <si>
+    <t>0.373</t>
+  </si>
+  <si>
+    <t>von Bertalannfy L-infinity (asymptotic length)</t>
+  </si>
+  <si>
+    <t>L50_Linf</t>
+  </si>
+  <si>
+    <t>312.27</t>
+  </si>
+  <si>
+    <t>Length at 50% maturity relative to asymptotic length (von B. L-infinity)</t>
+  </si>
+  <si>
+    <t>Total_L5_L50</t>
+  </si>
+  <si>
+    <t>0.56</t>
+  </si>
+  <si>
+    <t>Length at 5% selection relative to length at 50% maturity</t>
+  </si>
+  <si>
+    <t>Fleet selectivity</t>
+  </si>
+  <si>
+    <t>All fleets combined</t>
+  </si>
+  <si>
+    <t>Total_LFS_L50</t>
+  </si>
+  <si>
+    <t>0.964</t>
+  </si>
+  <si>
+    <t>Length at full selection relative to length at 50% maturity</t>
+  </si>
+  <si>
+    <t>Total_VML</t>
+  </si>
+  <si>
+    <t>0.359</t>
+  </si>
+  <si>
+    <t>Selectivity of maximum length class</t>
+  </si>
+  <si>
+    <t>Fleet_1_L5_L50</t>
+  </si>
+  <si>
+    <t>0.501</t>
+  </si>
+  <si>
+    <t>Fleet 1</t>
+  </si>
+  <si>
+    <t>Fleet_1_LFS_L50</t>
+  </si>
+  <si>
+    <t>0.732</t>
+  </si>
+  <si>
+    <t>Fleet_1_VML</t>
+  </si>
+  <si>
+    <t>0.215</t>
+  </si>
+  <si>
+    <t>Fleet_2_L5_L50</t>
+  </si>
+  <si>
+    <t>0.625</t>
+  </si>
+  <si>
+    <t>Fleet 2</t>
+  </si>
+  <si>
+    <t>Fleet_2_LFS_L50</t>
+  </si>
+  <si>
+    <t>0.719</t>
+  </si>
+  <si>
+    <t>Fleet_2_VML</t>
+  </si>
+  <si>
+    <t>0.07</t>
+  </si>
+  <si>
+    <t>Fleet_3_L5_L50</t>
+  </si>
+  <si>
+    <t>0.585</t>
+  </si>
+  <si>
+    <t>Fleet 3</t>
+  </si>
+  <si>
+    <t>Fleet_3_LFS_L50</t>
+  </si>
+  <si>
+    <t>1.15</t>
+  </si>
+  <si>
+    <t>Fleet_3_VML</t>
+  </si>
+  <si>
+    <t>0.435</t>
+  </si>
+  <si>
+    <t>Fleet_1_CF</t>
+  </si>
+  <si>
+    <t>0.209</t>
+  </si>
+  <si>
+    <t>Fraction of all historical catches that were Fleet 1</t>
+  </si>
+  <si>
+    <t>Fleet catch scale</t>
+  </si>
+  <si>
+    <t>Fleet_2_CF</t>
+  </si>
+  <si>
+    <t>0.053</t>
+  </si>
+  <si>
+    <t>Fraction of all historical catches that were Fleet 2</t>
+  </si>
+  <si>
+    <t>Fleet_3_CF</t>
+  </si>
+  <si>
+    <t>0.738</t>
+  </si>
+  <si>
+    <t>Fraction of all historical catches that were Fleet 3</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Total_catch</t>
+  </si>
+  <si>
+    <t>Total_mean_len</t>
+  </si>
+  <si>
+    <t>Total_mean_age</t>
+  </si>
+  <si>
+    <t>Total_CV_len</t>
+  </si>
+  <si>
+    <t>Total_frac_mat</t>
+  </si>
+  <si>
+    <t>Total_Index</t>
+  </si>
+  <si>
+    <t>Fleet_1_catch</t>
+  </si>
+  <si>
+    <t>Fleet_1_mean_len</t>
+  </si>
+  <si>
+    <t>Fleet_1_mean_age</t>
+  </si>
+  <si>
+    <t>Fleet_1_CV_len</t>
+  </si>
+  <si>
+    <t>Fleet_1_frac_mat</t>
+  </si>
+  <si>
+    <t>Fleet_1_Index</t>
+  </si>
+  <si>
+    <t>Fleet_2_catch</t>
+  </si>
+  <si>
+    <t>Fleet_2_mean_len</t>
+  </si>
+  <si>
+    <t>Fleet_2_mean_age</t>
+  </si>
+  <si>
+    <t>Fleet_2_CV_len</t>
+  </si>
+  <si>
+    <t>Fleet_2_frac_mat</t>
+  </si>
+  <si>
+    <t>Fleet_2_Index</t>
+  </si>
+  <si>
+    <t>Fleet_3_catch</t>
+  </si>
+  <si>
+    <t>Fleet_3_mean_len</t>
+  </si>
+  <si>
+    <t>Fleet_3_mean_age</t>
+  </si>
+  <si>
+    <t>Fleet_3_CV_len</t>
+  </si>
+  <si>
+    <t>Fleet_3_frac_mat</t>
+  </si>
+  <si>
+    <t>Fleet_3_Index</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -64,13 +342,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -108,7 +394,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -142,6 +428,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -176,9 +463,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -351,656 +639,368 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.54296875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Swordfish_NAtl</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Genus specius</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Billfish</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>North Atlantic</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>max_age</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>14.979</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Age to 5% natural survival</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Life history</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0.093</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>von Bertalannfy K</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Life history</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>L50_Linf</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.373</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Length at 50% maturity relative to asymptotic length (von B. L-infinity)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Life history</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>All_L5_L50</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Length at 5% selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>All fleets combined</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>All_LFS_L50</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0.964</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Length at full selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>All fleets combined</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>All_VML</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>0.359</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Selectivity of maximum length class</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>All fleets combined</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Fleet_1_L5_L50</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>0.501</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Length at 5% selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Fleet_1_LFS_L50</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>0.732</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Length at full selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Fleet_1_VML</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>0.215</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Selectivity of maximum length class</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fleet_2_L5_L50</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>0.625</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Length at 5% selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Fleet_2_LFS_L50</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0.719</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Length at full selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fleet_2_VML</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Selectivity of maximum length class</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Fleet_3_L5_L50</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>0.585</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Length at 5% selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Fleet_3_LFS_L50</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Length at full selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Fleet_3_VML</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>0.435</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Selectivity of maximum length class</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>All_ML_Linf</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.483</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Last historical mean length relative to Linf (e.g. mulen(2024) / Linf)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Fleet catch-length</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>All fleets combined</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Fleet_1_ML_Linf</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Last historical mean length relative to Linf (e.g. mulen(2024) / Linf)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Fleet catch-length</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Fleet_2_ML_Linf</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0.467</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Last historical mean length relative to Linf (e.g. mulen(2024) / Linf)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Fleet catch-length</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Fleet_3_ML_Linf</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>0.524</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Last historical mean length relative to Linf (e.g. mulen(2024) / Linf)</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Fleet catch-length</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Fleet_1_CF</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>0.209</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Fraction of all historical catches that were Fleet 1</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Fleet catch scale</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Fleet_2_CF</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>0.053</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Fraction of all historical catches that were Fleet 2</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Fleet catch scale</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Fleet_3_CF</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>0.738</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Fraction of all historical catches that were Fleet 3</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Fleet catch scale</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1009,138 +1009,88 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Y72"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Total_catch</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Total_mean_len</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Total_mean_age</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Total_CV_len</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Total_frac_mat</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Total_Index</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_catch</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_mean_len</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_mean_age</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_CV_len</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_frac_mat</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_Index</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_catch</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_mean_len</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_mean_age</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_CV_len</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_frac_mat</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_Index</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_catch</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_mean_len</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_mean_age</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_CV_len</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_frac_mat</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_Index</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1950</v>
       </c>
@@ -1160,7 +1110,7 @@
         <v>3646</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1951</v>
       </c>
@@ -1180,7 +1130,7 @@
         <v>2581</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1952</v>
       </c>
@@ -1200,7 +1150,7 @@
         <v>2993</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1953</v>
       </c>
@@ -1208,7 +1158,7 @@
         <v>3303</v>
       </c>
       <c r="G5">
-        <v>1.882</v>
+        <v>1.8819999999999999</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1220,7 +1170,7 @@
         <v>3303</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1954</v>
       </c>
@@ -1240,7 +1190,7 @@
         <v>3034</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1955</v>
       </c>
@@ -1260,7 +1210,7 @@
         <v>3502</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1956</v>
       </c>
@@ -1268,7 +1218,7 @@
         <v>3358</v>
       </c>
       <c r="G8">
-        <v>1.818</v>
+        <v>1.8180000000000001</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1280,7 +1230,7 @@
         <v>3358</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1957</v>
       </c>
@@ -1300,7 +1250,7 @@
         <v>4578</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1958</v>
       </c>
@@ -1320,7 +1270,7 @@
         <v>4904</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1959</v>
       </c>
@@ -1340,7 +1290,7 @@
         <v>6232</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1960</v>
       </c>
@@ -1348,7 +1298,7 @@
         <v>3828</v>
       </c>
       <c r="G12">
-        <v>1.731</v>
+        <v>1.7310000000000001</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1360,7 +1310,7 @@
         <v>3828</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1961</v>
       </c>
@@ -1380,7 +1330,7 @@
         <v>4381</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1962</v>
       </c>
@@ -1388,7 +1338,7 @@
         <v>5342</v>
       </c>
       <c r="G14">
-        <v>1.674</v>
+        <v>1.6739999999999999</v>
       </c>
       <c r="H14">
         <v>65</v>
@@ -1400,10 +1350,10 @@
         <v>5277</v>
       </c>
       <c r="Y14">
-        <v>0.026</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>2.5999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1963</v>
       </c>
@@ -1411,7 +1361,7 @@
         <v>10190</v>
       </c>
       <c r="G15">
-        <v>1.664</v>
+        <v>1.6639999999999999</v>
       </c>
       <c r="H15">
         <v>1053</v>
@@ -1423,10 +1373,10 @@
         <v>9137</v>
       </c>
       <c r="Y15">
-        <v>11.332</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>11.332000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1964</v>
       </c>
@@ -1446,10 +1396,10 @@
         <v>9979</v>
       </c>
       <c r="Y16">
-        <v>3.986</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>3.9860000000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1965</v>
       </c>
@@ -1457,7 +1407,7 @@
         <v>8652</v>
       </c>
       <c r="G17">
-        <v>1.638</v>
+        <v>1.6379999999999999</v>
       </c>
       <c r="H17">
         <v>945</v>
@@ -1469,10 +1419,10 @@
         <v>7707</v>
       </c>
       <c r="Y17">
-        <v>2.461</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>2.4609999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>1966</v>
       </c>
@@ -1480,7 +1430,7 @@
         <v>9349</v>
       </c>
       <c r="G18">
-        <v>1.584</v>
+        <v>1.5840000000000001</v>
       </c>
       <c r="H18">
         <v>534</v>
@@ -1492,10 +1442,10 @@
         <v>8815</v>
       </c>
       <c r="Y18">
-        <v>2.485</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>2.4849999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1967</v>
       </c>
@@ -1515,10 +1465,10 @@
         <v>8767</v>
       </c>
       <c r="Y19">
-        <v>2.914</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>2.9140000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>1968</v>
       </c>
@@ -1541,7 +1491,7 @@
         <v>1.556</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>1969</v>
       </c>
@@ -1564,7 +1514,7 @@
         <v>1.421</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>1970</v>
       </c>
@@ -1572,25 +1522,25 @@
         <v>9578</v>
       </c>
       <c r="C22">
-        <v>154.764</v>
+        <v>154.76400000000001</v>
       </c>
       <c r="E22">
-        <v>0.196</v>
+        <v>0.19600000000000001</v>
       </c>
       <c r="F22">
         <v>0.876</v>
       </c>
       <c r="G22">
-        <v>1.414</v>
+        <v>1.4139999999999999</v>
       </c>
       <c r="H22">
         <v>287</v>
       </c>
       <c r="I22">
-        <v>154.764</v>
+        <v>154.76400000000001</v>
       </c>
       <c r="K22">
-        <v>0.196</v>
+        <v>0.19600000000000001</v>
       </c>
       <c r="L22">
         <v>0.876</v>
@@ -1602,10 +1552,10 @@
         <v>9291</v>
       </c>
       <c r="Y22">
-        <v>1.612</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>1.6120000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>1971</v>
       </c>
@@ -1613,13 +1563,13 @@
         <v>5266</v>
       </c>
       <c r="C23">
-        <v>140.009</v>
+        <v>140.00899999999999</v>
       </c>
       <c r="E23">
-        <v>0.288</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="F23">
-        <v>0.704</v>
+        <v>0.70399999999999996</v>
       </c>
       <c r="G23">
         <v>1.381</v>
@@ -1634,19 +1584,19 @@
         <v>5231</v>
       </c>
       <c r="U23">
-        <v>140.009</v>
+        <v>140.00899999999999</v>
       </c>
       <c r="W23">
-        <v>0.288</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="X23">
-        <v>0.704</v>
+        <v>0.70399999999999996</v>
       </c>
       <c r="Y23">
-        <v>0.034</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>3.4000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>1972</v>
       </c>
@@ -1654,13 +1604,13 @@
         <v>4766</v>
       </c>
       <c r="C24">
-        <v>161.02</v>
+        <v>161.02000000000001</v>
       </c>
       <c r="E24">
         <v>0.22</v>
       </c>
       <c r="F24">
-        <v>0.888</v>
+        <v>0.88800000000000001</v>
       </c>
       <c r="G24">
         <v>1.351</v>
@@ -1675,19 +1625,19 @@
         <v>4520</v>
       </c>
       <c r="U24">
-        <v>161.02</v>
+        <v>161.02000000000001</v>
       </c>
       <c r="W24">
         <v>0.22</v>
       </c>
       <c r="X24">
-        <v>0.888</v>
+        <v>0.88800000000000001</v>
       </c>
       <c r="Y24">
-        <v>0.032</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>3.2000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>1973</v>
       </c>
@@ -1707,10 +1657,10 @@
         <v>5668</v>
       </c>
       <c r="Y25">
-        <v>0.034</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>3.4000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>1974</v>
       </c>
@@ -1718,28 +1668,28 @@
         <v>6362</v>
       </c>
       <c r="C26">
-        <v>143.765</v>
+        <v>143.76499999999999</v>
       </c>
       <c r="E26">
-        <v>0.234</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="F26">
-        <v>0.733</v>
+        <v>0.73299999999999998</v>
       </c>
       <c r="G26">
-        <v>1.324</v>
+        <v>1.3240000000000001</v>
       </c>
       <c r="H26">
         <v>1125</v>
       </c>
       <c r="I26">
-        <v>143.765</v>
+        <v>143.76499999999999</v>
       </c>
       <c r="K26">
-        <v>0.234</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="L26">
-        <v>0.733</v>
+        <v>0.73299999999999998</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -1748,10 +1698,10 @@
         <v>5237</v>
       </c>
       <c r="Y26">
-        <v>0.032</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>3.2000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>1975</v>
       </c>
@@ -1765,7 +1715,7 @@
         <v>0.222</v>
       </c>
       <c r="F27">
-        <v>0.896</v>
+        <v>0.89600000000000002</v>
       </c>
       <c r="G27">
         <v>1.333</v>
@@ -1774,13 +1724,13 @@
         <v>1700</v>
       </c>
       <c r="I27">
-        <v>150.617</v>
+        <v>150.61699999999999</v>
       </c>
       <c r="K27">
         <v>0.218</v>
       </c>
       <c r="L27">
-        <v>0.827</v>
+        <v>0.82699999999999996</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -1789,19 +1739,19 @@
         <v>7139</v>
       </c>
       <c r="U27">
-        <v>193.407</v>
+        <v>193.40700000000001</v>
       </c>
       <c r="W27">
-        <v>0.227</v>
+        <v>0.22700000000000001</v>
       </c>
       <c r="X27">
-        <v>0.965</v>
+        <v>0.96499999999999997</v>
       </c>
       <c r="Y27">
         <v>4.218</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>1976</v>
       </c>
@@ -1809,16 +1759,16 @@
         <v>6696</v>
       </c>
       <c r="C28">
-        <v>164.421</v>
+        <v>164.42099999999999</v>
       </c>
       <c r="E28">
         <v>0.219</v>
       </c>
       <c r="F28">
-        <v>0.881</v>
+        <v>0.88100000000000001</v>
       </c>
       <c r="G28">
-        <v>1.336</v>
+        <v>1.3360000000000001</v>
       </c>
       <c r="H28">
         <v>1429</v>
@@ -1830,7 +1780,7 @@
         <v>0.222</v>
       </c>
       <c r="L28">
-        <v>0.796</v>
+        <v>0.79600000000000004</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -1839,19 +1789,19 @@
         <v>5267</v>
       </c>
       <c r="U28">
-        <v>181.781</v>
+        <v>181.78100000000001</v>
       </c>
       <c r="W28">
         <v>0.217</v>
       </c>
       <c r="X28">
-        <v>0.966</v>
+        <v>0.96599999999999997</v>
       </c>
       <c r="Y28">
-        <v>2.305</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>2.3050000000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>1977</v>
       </c>
@@ -1859,28 +1809,28 @@
         <v>6409</v>
       </c>
       <c r="C29">
-        <v>161.978</v>
+        <v>161.97800000000001</v>
       </c>
       <c r="E29">
-        <v>0.207</v>
+        <v>0.20699999999999999</v>
       </c>
       <c r="F29">
-        <v>0.897</v>
+        <v>0.89700000000000002</v>
       </c>
       <c r="G29">
-        <v>1.336</v>
+        <v>1.3360000000000001</v>
       </c>
       <c r="H29">
         <v>912</v>
       </c>
       <c r="I29">
-        <v>147.939</v>
+        <v>147.93899999999999</v>
       </c>
       <c r="K29">
         <v>0.222</v>
       </c>
       <c r="L29">
-        <v>0.8179999999999999</v>
+        <v>0.81799999999999995</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -1889,19 +1839,19 @@
         <v>5497</v>
       </c>
       <c r="U29">
-        <v>176.016</v>
+        <v>176.01599999999999</v>
       </c>
       <c r="W29">
         <v>0.191</v>
       </c>
       <c r="X29">
-        <v>0.976</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="Y29">
-        <v>2.662</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>2.6619999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>1978</v>
       </c>
@@ -1909,10 +1859,10 @@
         <v>11827</v>
       </c>
       <c r="C30">
-        <v>167.912</v>
+        <v>167.91200000000001</v>
       </c>
       <c r="E30">
-        <v>0.199</v>
+        <v>0.19900000000000001</v>
       </c>
       <c r="F30">
         <v>0.93</v>
@@ -1924,10 +1874,10 @@
         <v>3020</v>
       </c>
       <c r="I30">
-        <v>154.076</v>
+        <v>154.07599999999999</v>
       </c>
       <c r="K30">
-        <v>0.209</v>
+        <v>0.20899999999999999</v>
       </c>
       <c r="L30">
         <v>0.876</v>
@@ -1939,19 +1889,19 @@
         <v>8807</v>
       </c>
       <c r="U30">
-        <v>181.748</v>
+        <v>181.74799999999999</v>
       </c>
       <c r="W30">
         <v>0.188</v>
       </c>
       <c r="X30">
-        <v>0.983</v>
+        <v>0.98299999999999998</v>
       </c>
       <c r="Y30">
-        <v>3.038</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>3.0379999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>1979</v>
       </c>
@@ -1968,19 +1918,19 @@
         <v>0.84</v>
       </c>
       <c r="G31">
-        <v>1.317</v>
+        <v>1.3169999999999999</v>
       </c>
       <c r="H31">
         <v>3888</v>
       </c>
       <c r="I31">
-        <v>149.674</v>
+        <v>149.67400000000001</v>
       </c>
       <c r="K31">
         <v>0.252</v>
       </c>
       <c r="L31">
-        <v>0.773</v>
+        <v>0.77300000000000002</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -1992,16 +1942,16 @@
         <v>168.267</v>
       </c>
       <c r="W31">
-        <v>0.228</v>
+        <v>0.22800000000000001</v>
       </c>
       <c r="X31">
-        <v>0.907</v>
+        <v>0.90700000000000003</v>
       </c>
       <c r="Y31">
         <v>1.752</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>1980</v>
       </c>
@@ -2009,22 +1959,22 @@
         <v>13558</v>
       </c>
       <c r="C32">
-        <v>170.926</v>
+        <v>170.92599999999999</v>
       </c>
       <c r="E32">
-        <v>0.202</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="F32">
-        <v>0.896</v>
+        <v>0.89600000000000002</v>
       </c>
       <c r="G32">
-        <v>1.315</v>
+        <v>1.3149999999999999</v>
       </c>
       <c r="H32">
         <v>5015</v>
       </c>
       <c r="I32">
-        <v>144.722</v>
+        <v>144.72200000000001</v>
       </c>
       <c r="K32">
         <v>0.252</v>
@@ -2039,10 +1989,10 @@
         <v>8543</v>
       </c>
       <c r="U32">
-        <v>184.028</v>
+        <v>184.02799999999999</v>
       </c>
       <c r="W32">
-        <v>0.177</v>
+        <v>0.17699999999999999</v>
       </c>
       <c r="X32">
         <v>0.97</v>
@@ -2051,7 +2001,7 @@
         <v>1.758</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>1981</v>
       </c>
@@ -2059,13 +2009,13 @@
         <v>11197</v>
       </c>
       <c r="C33">
-        <v>169.618</v>
+        <v>169.61799999999999</v>
       </c>
       <c r="E33">
         <v>0.184</v>
       </c>
       <c r="F33">
-        <v>0.9379999999999999</v>
+        <v>0.93799999999999994</v>
       </c>
       <c r="G33">
         <v>1.276</v>
@@ -2095,13 +2045,13 @@
         <v>0.16</v>
       </c>
       <c r="X33">
-        <v>0.987</v>
+        <v>0.98699999999999999</v>
       </c>
       <c r="Y33">
         <v>1.617</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>1982</v>
       </c>
@@ -2109,10 +2059,10 @@
         <v>13215</v>
       </c>
       <c r="C34">
-        <v>172.835</v>
+        <v>172.83500000000001</v>
       </c>
       <c r="E34">
-        <v>0.206</v>
+        <v>0.20599999999999999</v>
       </c>
       <c r="F34">
         <v>0.91</v>
@@ -2124,13 +2074,13 @@
         <v>5271</v>
       </c>
       <c r="I34">
-        <v>145.168</v>
+        <v>145.16800000000001</v>
       </c>
       <c r="K34">
         <v>0.26</v>
       </c>
       <c r="L34">
-        <v>0.743</v>
+        <v>0.74299999999999999</v>
       </c>
       <c r="N34">
         <v>4</v>
@@ -2139,19 +2089,19 @@
         <v>7940</v>
       </c>
       <c r="U34">
-        <v>182.058</v>
+        <v>182.05799999999999</v>
       </c>
       <c r="W34">
         <v>0.189</v>
       </c>
       <c r="X34">
-        <v>0.966</v>
+        <v>0.96599999999999997</v>
       </c>
       <c r="Y34">
-        <v>0.711</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>0.71099999999999997</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>1983</v>
       </c>
@@ -2159,16 +2109,16 @@
         <v>14563</v>
       </c>
       <c r="C35">
-        <v>169.139</v>
+        <v>169.13900000000001</v>
       </c>
       <c r="E35">
         <v>0.184</v>
       </c>
       <c r="F35">
-        <v>0.898</v>
+        <v>0.89800000000000002</v>
       </c>
       <c r="G35">
-        <v>1.185</v>
+        <v>1.1850000000000001</v>
       </c>
       <c r="H35">
         <v>4510</v>
@@ -2177,10 +2127,10 @@
         <v>142.35</v>
       </c>
       <c r="K35">
-        <v>0.272</v>
+        <v>0.27200000000000002</v>
       </c>
       <c r="L35">
-        <v>0.6860000000000001</v>
+        <v>0.68600000000000005</v>
       </c>
       <c r="N35">
         <v>3</v>
@@ -2189,19 +2139,19 @@
         <v>10050</v>
       </c>
       <c r="U35">
-        <v>178.068</v>
+        <v>178.06800000000001</v>
       </c>
       <c r="W35">
         <v>0.154</v>
       </c>
       <c r="X35">
-        <v>0.968</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="Y35">
-        <v>0.572</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>0.57199999999999995</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>1984</v>
       </c>
@@ -2209,13 +2159,13 @@
         <v>12833</v>
       </c>
       <c r="C36">
-        <v>148.076</v>
+        <v>148.07599999999999</v>
       </c>
       <c r="E36">
         <v>0.22</v>
       </c>
       <c r="F36">
-        <v>0.823</v>
+        <v>0.82299999999999995</v>
       </c>
       <c r="G36">
         <v>1.145</v>
@@ -2224,7 +2174,7 @@
         <v>4666</v>
       </c>
       <c r="I36">
-        <v>136.878</v>
+        <v>136.87799999999999</v>
       </c>
       <c r="K36">
         <v>0.255</v>
@@ -2242,16 +2192,16 @@
         <v>151.809</v>
       </c>
       <c r="W36">
-        <v>0.208</v>
+        <v>0.20799999999999999</v>
       </c>
       <c r="X36">
         <v>0.873</v>
       </c>
       <c r="Y36">
-        <v>0.517</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>0.51700000000000002</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>1985</v>
       </c>
@@ -2262,7 +2212,7 @@
         <v>149.352</v>
       </c>
       <c r="E37">
-        <v>0.204</v>
+        <v>0.20399999999999999</v>
       </c>
       <c r="F37">
         <v>0.85</v>
@@ -2274,13 +2224,13 @@
         <v>4642</v>
       </c>
       <c r="I37">
-        <v>138.013</v>
+        <v>138.01300000000001</v>
       </c>
       <c r="K37">
         <v>0.255</v>
       </c>
       <c r="L37">
-        <v>0.6860000000000001</v>
+        <v>0.68600000000000005</v>
       </c>
       <c r="N37">
         <v>15</v>
@@ -2295,13 +2245,13 @@
         <v>0.187</v>
       </c>
       <c r="X37">
-        <v>0.905</v>
+        <v>0.90500000000000003</v>
       </c>
       <c r="Y37">
         <v>0.59</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>1986</v>
       </c>
@@ -2315,7 +2265,7 @@
         <v>0.183</v>
       </c>
       <c r="F38">
-        <v>0.867</v>
+        <v>0.86699999999999999</v>
       </c>
       <c r="G38">
         <v>1.008</v>
@@ -2330,7 +2280,7 @@
         <v>0.248</v>
       </c>
       <c r="L38">
-        <v>0.655</v>
+        <v>0.65500000000000003</v>
       </c>
       <c r="N38">
         <v>448</v>
@@ -2342,16 +2292,16 @@
         <v>159.779</v>
       </c>
       <c r="W38">
-        <v>0.167</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="X38">
         <v>0.92</v>
       </c>
       <c r="Y38">
-        <v>0.519</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>0.51900000000000002</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>1987</v>
       </c>
@@ -2362,19 +2312,19 @@
         <v>153.011</v>
       </c>
       <c r="E39">
-        <v>0.241</v>
+        <v>0.24099999999999999</v>
       </c>
       <c r="F39">
-        <v>0.776</v>
+        <v>0.77600000000000002</v>
       </c>
       <c r="G39">
-        <v>0.9350000000000001</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="H39">
         <v>5164</v>
       </c>
       <c r="I39">
-        <v>130.561</v>
+        <v>130.56100000000001</v>
       </c>
       <c r="K39">
         <v>0.247</v>
@@ -2386,7 +2336,7 @@
         <v>984</v>
       </c>
       <c r="O39">
-        <v>143.007</v>
+        <v>143.00700000000001</v>
       </c>
       <c r="Q39">
         <v>0.255</v>
@@ -2401,16 +2351,16 @@
         <v>161.125</v>
       </c>
       <c r="W39">
-        <v>0.236</v>
+        <v>0.23599999999999999</v>
       </c>
       <c r="X39">
-        <v>0.824</v>
+        <v>0.82399999999999995</v>
       </c>
       <c r="Y39">
-        <v>0.424</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>0.42399999999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>1988</v>
       </c>
@@ -2418,16 +2368,16 @@
         <v>19525</v>
       </c>
       <c r="C40">
-        <v>153.924</v>
+        <v>153.92400000000001</v>
       </c>
       <c r="E40">
-        <v>0.203</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="F40">
-        <v>0.821</v>
+        <v>0.82099999999999995</v>
       </c>
       <c r="G40">
-        <v>0.856</v>
+        <v>0.85599999999999998</v>
       </c>
       <c r="H40">
         <v>6020</v>
@@ -2439,7 +2389,7 @@
         <v>0.247</v>
       </c>
       <c r="L40">
-        <v>0.577</v>
+        <v>0.57699999999999996</v>
       </c>
       <c r="N40">
         <v>612</v>
@@ -2448,19 +2398,19 @@
         <v>12893</v>
       </c>
       <c r="U40">
-        <v>160.669</v>
+        <v>160.66900000000001</v>
       </c>
       <c r="W40">
         <v>0.192</v>
       </c>
       <c r="X40">
-        <v>0.882</v>
+        <v>0.88200000000000001</v>
       </c>
       <c r="Y40">
         <v>0.439</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>1989</v>
       </c>
@@ -2471,25 +2421,25 @@
         <v>157.244</v>
       </c>
       <c r="E41">
-        <v>0.201</v>
+        <v>0.20100000000000001</v>
       </c>
       <c r="F41">
-        <v>0.827</v>
+        <v>0.82699999999999996</v>
       </c>
       <c r="G41">
-        <v>0.766</v>
+        <v>0.76600000000000001</v>
       </c>
       <c r="H41">
         <v>5855</v>
       </c>
       <c r="I41">
-        <v>128.367</v>
+        <v>128.36699999999999</v>
       </c>
       <c r="K41">
-        <v>0.244</v>
+        <v>0.24399999999999999</v>
       </c>
       <c r="L41">
-        <v>0.585</v>
+        <v>0.58499999999999996</v>
       </c>
       <c r="N41">
         <v>292</v>
@@ -2498,19 +2448,19 @@
         <v>11114</v>
       </c>
       <c r="U41">
-        <v>164.463</v>
+        <v>164.46299999999999</v>
       </c>
       <c r="W41">
         <v>0.19</v>
       </c>
       <c r="X41">
-        <v>0.888</v>
+        <v>0.88800000000000001</v>
       </c>
       <c r="Y41">
-        <v>0.383</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>0.38300000000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>1990</v>
       </c>
@@ -2518,16 +2468,16 @@
         <v>15672</v>
       </c>
       <c r="C42">
-        <v>154.486</v>
+        <v>154.48599999999999</v>
       </c>
       <c r="E42">
-        <v>0.177</v>
+        <v>0.17699999999999999</v>
       </c>
       <c r="F42">
         <v>0.86</v>
       </c>
       <c r="G42">
-        <v>0.681</v>
+        <v>0.68100000000000005</v>
       </c>
       <c r="H42">
         <v>4967</v>
@@ -2539,37 +2489,37 @@
         <v>0.24</v>
       </c>
       <c r="L42">
-        <v>0.632</v>
+        <v>0.63200000000000001</v>
       </c>
       <c r="N42">
         <v>463</v>
       </c>
       <c r="O42">
-        <v>131.3</v>
+        <v>131.30000000000001</v>
       </c>
       <c r="Q42">
-        <v>0.175</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="R42">
-        <v>0.703</v>
+        <v>0.70299999999999996</v>
       </c>
       <c r="T42">
         <v>10242</v>
       </c>
       <c r="U42">
-        <v>163.955</v>
+        <v>163.95500000000001</v>
       </c>
       <c r="W42">
-        <v>0.164</v>
+        <v>0.16400000000000001</v>
       </c>
       <c r="X42">
-        <v>0.9370000000000001</v>
+        <v>0.93700000000000006</v>
       </c>
       <c r="Y42">
-        <v>0.479</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>0.47899999999999998</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>1991</v>
       </c>
@@ -2580,10 +2530,10 @@
         <v>161.392</v>
       </c>
       <c r="E43">
-        <v>0.178</v>
+        <v>0.17799999999999999</v>
       </c>
       <c r="F43">
-        <v>0.917</v>
+        <v>0.91700000000000004</v>
       </c>
       <c r="G43">
         <v>0.61</v>
@@ -2595,7 +2545,7 @@
         <v>137.023</v>
       </c>
       <c r="K43">
-        <v>0.227</v>
+        <v>0.22700000000000001</v>
       </c>
       <c r="L43">
         <v>0.746</v>
@@ -2607,19 +2557,19 @@
         <v>9778</v>
       </c>
       <c r="U43">
-        <v>166.266</v>
+        <v>166.26599999999999</v>
       </c>
       <c r="W43">
-        <v>0.168</v>
+        <v>0.16800000000000001</v>
       </c>
       <c r="X43">
-        <v>0.951</v>
+        <v>0.95099999999999996</v>
       </c>
       <c r="Y43">
-        <v>0.481</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>0.48099999999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>1992</v>
       </c>
@@ -2630,25 +2580,25 @@
         <v>162.376</v>
       </c>
       <c r="E44">
-        <v>0.173</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="F44">
-        <v>0.925</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="G44">
-        <v>0.555</v>
+        <v>0.55500000000000005</v>
       </c>
       <c r="H44">
         <v>4124</v>
       </c>
       <c r="I44">
-        <v>145.08</v>
+        <v>145.08000000000001</v>
       </c>
       <c r="K44">
         <v>0.187</v>
       </c>
       <c r="L44">
-        <v>0.894</v>
+        <v>0.89400000000000002</v>
       </c>
       <c r="N44">
         <v>497</v>
@@ -2657,19 +2607,19 @@
         <v>10773</v>
       </c>
       <c r="U44">
-        <v>165.835</v>
+        <v>165.83500000000001</v>
       </c>
       <c r="W44">
         <v>0.17</v>
       </c>
       <c r="X44">
-        <v>0.931</v>
+        <v>0.93100000000000005</v>
       </c>
       <c r="Y44">
-        <v>0.403</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>0.40300000000000002</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>1993</v>
       </c>
@@ -2683,10 +2633,10 @@
         <v>0.19</v>
       </c>
       <c r="F45">
-        <v>0.773</v>
+        <v>0.77300000000000002</v>
       </c>
       <c r="G45">
-        <v>0.517</v>
+        <v>0.51700000000000002</v>
       </c>
       <c r="H45">
         <v>4044</v>
@@ -2698,10 +2648,10 @@
         <v>0.189</v>
       </c>
       <c r="L45">
-        <v>0.507</v>
+        <v>0.50700000000000001</v>
       </c>
       <c r="M45">
-        <v>0.904</v>
+        <v>0.90400000000000003</v>
       </c>
       <c r="N45">
         <v>1950</v>
@@ -2713,7 +2663,7 @@
         <v>0.252</v>
       </c>
       <c r="R45">
-        <v>0.545</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="T45">
         <v>10744</v>
@@ -2722,16 +2672,16 @@
         <v>162.755</v>
       </c>
       <c r="W45">
-        <v>0.178</v>
+        <v>0.17799999999999999</v>
       </c>
       <c r="X45">
-        <v>0.925</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="Y45">
-        <v>0.394</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>0.39400000000000002</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>1994</v>
       </c>
@@ -2742,10 +2692,10 @@
         <v>150.685</v>
       </c>
       <c r="E46">
-        <v>0.172</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="F46">
-        <v>0.787</v>
+        <v>0.78700000000000003</v>
       </c>
       <c r="G46">
         <v>0.49</v>
@@ -2757,13 +2707,13 @@
         <v>122.405</v>
       </c>
       <c r="K46">
-        <v>0.167</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="L46">
-        <v>0.517</v>
+        <v>0.51700000000000002</v>
       </c>
       <c r="M46">
-        <v>0.944</v>
+        <v>0.94399999999999995</v>
       </c>
       <c r="N46">
         <v>1579</v>
@@ -2772,28 +2722,28 @@
         <v>126.521</v>
       </c>
       <c r="Q46">
-        <v>0.174</v>
+        <v>0.17399999999999999</v>
       </c>
       <c r="R46">
-        <v>0.604</v>
+        <v>0.60399999999999998</v>
       </c>
       <c r="T46">
         <v>9962</v>
       </c>
       <c r="U46">
-        <v>166.829</v>
+        <v>166.82900000000001</v>
       </c>
       <c r="W46">
-        <v>0.173</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="X46">
-        <v>0.931</v>
+        <v>0.93100000000000005</v>
       </c>
       <c r="Y46">
-        <v>0.327</v>
-      </c>
-    </row>
-    <row r="47">
+        <v>0.32700000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>1995</v>
       </c>
@@ -2801,31 +2751,31 @@
         <v>17105</v>
       </c>
       <c r="C47">
-        <v>149.248</v>
+        <v>149.24799999999999</v>
       </c>
       <c r="E47">
-        <v>0.176</v>
+        <v>0.17599999999999999</v>
       </c>
       <c r="F47">
         <v>0.8</v>
       </c>
       <c r="G47">
-        <v>0.464</v>
+        <v>0.46400000000000002</v>
       </c>
       <c r="H47">
         <v>4452</v>
       </c>
       <c r="I47">
-        <v>122.204</v>
+        <v>122.20399999999999</v>
       </c>
       <c r="K47">
-        <v>0.179</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="L47">
-        <v>0.535</v>
+        <v>0.53500000000000003</v>
       </c>
       <c r="M47">
-        <v>0.954</v>
+        <v>0.95399999999999996</v>
       </c>
       <c r="N47">
         <v>1593</v>
@@ -2834,28 +2784,28 @@
         <v>126.997</v>
       </c>
       <c r="Q47">
-        <v>0.181</v>
+        <v>0.18099999999999999</v>
       </c>
       <c r="R47">
-        <v>0.646</v>
+        <v>0.64600000000000002</v>
       </c>
       <c r="T47">
         <v>11060</v>
       </c>
       <c r="U47">
-        <v>164.515</v>
+        <v>164.51499999999999</v>
       </c>
       <c r="W47">
-        <v>0.173</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="X47">
-        <v>0.9370000000000001</v>
+        <v>0.93700000000000006</v>
       </c>
       <c r="Y47">
-        <v>0.355</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>0.35499999999999998</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>1996</v>
       </c>
@@ -2866,13 +2816,13 @@
         <v>154.875</v>
       </c>
       <c r="E48">
-        <v>0.163</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="F48">
-        <v>0.8120000000000001</v>
+        <v>0.81200000000000006</v>
       </c>
       <c r="G48">
-        <v>0.423</v>
+        <v>0.42299999999999999</v>
       </c>
       <c r="H48">
         <v>4015</v>
@@ -2896,19 +2846,19 @@
         <v>9505</v>
       </c>
       <c r="U48">
-        <v>167.617</v>
+        <v>167.61699999999999</v>
       </c>
       <c r="W48">
-        <v>0.167</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="X48">
-        <v>0.9389999999999999</v>
+        <v>0.93899999999999995</v>
       </c>
       <c r="Y48">
-        <v>0.266</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>0.26600000000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>1997</v>
       </c>
@@ -2916,31 +2866,31 @@
         <v>13025</v>
       </c>
       <c r="C49">
-        <v>153.789</v>
+        <v>153.78899999999999</v>
       </c>
       <c r="E49">
-        <v>0.175</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="F49">
-        <v>0.792</v>
+        <v>0.79200000000000004</v>
       </c>
       <c r="G49">
-        <v>0.389</v>
+        <v>0.38900000000000001</v>
       </c>
       <c r="H49">
         <v>3399</v>
       </c>
       <c r="I49">
-        <v>122.894</v>
+        <v>122.89400000000001</v>
       </c>
       <c r="K49">
-        <v>0.173</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="L49">
-        <v>0.515</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="M49">
-        <v>0.954</v>
+        <v>0.95399999999999996</v>
       </c>
       <c r="N49">
         <v>902</v>
@@ -2949,19 +2899,19 @@
         <v>8724</v>
       </c>
       <c r="U49">
-        <v>166.147</v>
+        <v>166.14699999999999</v>
       </c>
       <c r="W49">
-        <v>0.176</v>
+        <v>0.17599999999999999</v>
       </c>
       <c r="X49">
-        <v>0.903</v>
+        <v>0.90300000000000002</v>
       </c>
       <c r="Y49">
-        <v>0.274</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>0.27400000000000002</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>1998</v>
       </c>
@@ -2972,13 +2922,13 @@
         <v>148.411</v>
       </c>
       <c r="E50">
-        <v>0.167</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="F50">
-        <v>0.771</v>
+        <v>0.77100000000000002</v>
       </c>
       <c r="G50">
-        <v>0.349</v>
+        <v>0.34899999999999998</v>
       </c>
       <c r="H50">
         <v>3433</v>
@@ -2987,10 +2937,10 @@
         <v>123.759</v>
       </c>
       <c r="K50">
-        <v>0.145</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="L50">
-        <v>0.517</v>
+        <v>0.51700000000000002</v>
       </c>
       <c r="M50">
         <v>1.35</v>
@@ -2999,31 +2949,31 @@
         <v>772</v>
       </c>
       <c r="O50">
-        <v>123.832</v>
+        <v>123.83199999999999</v>
       </c>
       <c r="Q50">
         <v>0.22</v>
       </c>
       <c r="R50">
-        <v>0.518</v>
+        <v>0.51800000000000002</v>
       </c>
       <c r="T50">
         <v>8124</v>
       </c>
       <c r="U50">
-        <v>163.188</v>
+        <v>163.18799999999999</v>
       </c>
       <c r="W50">
-        <v>0.165</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="X50">
-        <v>0.923</v>
+        <v>0.92300000000000004</v>
       </c>
       <c r="Y50">
         <v>0.316</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>1999</v>
       </c>
@@ -3031,13 +2981,13 @@
         <v>11622</v>
       </c>
       <c r="C51">
-        <v>145.157</v>
+        <v>145.15700000000001</v>
       </c>
       <c r="E51">
-        <v>0.175</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="F51">
-        <v>0.777</v>
+        <v>0.77700000000000002</v>
       </c>
       <c r="G51">
         <v>0.318</v>
@@ -3046,13 +2996,13 @@
         <v>3364</v>
       </c>
       <c r="I51">
-        <v>121.957</v>
+        <v>121.95699999999999</v>
       </c>
       <c r="K51">
-        <v>0.172</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="L51">
-        <v>0.491</v>
+        <v>0.49099999999999999</v>
       </c>
       <c r="M51">
         <v>1.33</v>
@@ -3061,34 +3011,34 @@
         <v>776</v>
       </c>
       <c r="O51">
-        <v>125.216</v>
+        <v>125.21599999999999</v>
       </c>
       <c r="Q51">
-        <v>0.234</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="R51">
-        <v>0.586</v>
+        <v>0.58599999999999997</v>
       </c>
       <c r="S51">
-        <v>0.5590000000000001</v>
+        <v>0.55900000000000005</v>
       </c>
       <c r="T51">
         <v>7482</v>
       </c>
       <c r="U51">
-        <v>158.425</v>
+        <v>158.42500000000001</v>
       </c>
       <c r="W51">
-        <v>0.164</v>
+        <v>0.16400000000000001</v>
       </c>
       <c r="X51">
-        <v>0.929</v>
+        <v>0.92900000000000005</v>
       </c>
       <c r="Y51">
-        <v>0.342</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>0.34200000000000003</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>2000</v>
       </c>
@@ -3096,16 +3046,16 @@
         <v>12051.367</v>
       </c>
       <c r="C52">
-        <v>146.519</v>
+        <v>146.51900000000001</v>
       </c>
       <c r="E52">
-        <v>0.173</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="F52">
-        <v>0.759</v>
+        <v>0.75900000000000001</v>
       </c>
       <c r="G52">
-        <v>0.299</v>
+        <v>0.29899999999999999</v>
       </c>
       <c r="H52">
         <v>3315.71</v>
@@ -3114,13 +3064,13 @@
         <v>122.986</v>
       </c>
       <c r="K52">
-        <v>0.174</v>
+        <v>0.17399999999999999</v>
       </c>
       <c r="L52">
         <v>0.498</v>
       </c>
       <c r="M52">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="N52">
         <v>731</v>
@@ -3138,54 +3088,54 @@
         <v>0.82</v>
       </c>
       <c r="T52">
-        <v>8004.657</v>
+        <v>8004.6570000000002</v>
       </c>
       <c r="U52">
-        <v>163.436</v>
+        <v>163.43600000000001</v>
       </c>
       <c r="W52">
-        <v>0.168</v>
+        <v>0.16800000000000001</v>
       </c>
       <c r="X52">
-        <v>0.922</v>
+        <v>0.92200000000000004</v>
       </c>
       <c r="Y52">
-        <v>0.381</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>0.38100000000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>2001</v>
       </c>
       <c r="B53">
-        <v>10577.853</v>
+        <v>10577.852999999999</v>
       </c>
       <c r="C53">
-        <v>145.217</v>
+        <v>145.21700000000001</v>
       </c>
       <c r="E53">
-        <v>0.196</v>
+        <v>0.19600000000000001</v>
       </c>
       <c r="F53">
-        <v>0.739</v>
+        <v>0.73899999999999999</v>
       </c>
       <c r="G53">
-        <v>0.286</v>
+        <v>0.28599999999999998</v>
       </c>
       <c r="H53">
         <v>2497.96</v>
       </c>
       <c r="I53">
-        <v>118.609</v>
+        <v>118.60899999999999</v>
       </c>
       <c r="K53">
-        <v>0.207</v>
+        <v>0.20699999999999999</v>
       </c>
       <c r="L53">
-        <v>0.489</v>
+        <v>0.48899999999999999</v>
       </c>
       <c r="M53">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="N53">
         <v>731</v>
@@ -3197,10 +3147,10 @@
         <v>0.215</v>
       </c>
       <c r="R53">
-        <v>0.545</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="S53">
-        <v>0.642</v>
+        <v>0.64200000000000002</v>
       </c>
       <c r="T53">
         <v>7348.893</v>
@@ -3212,30 +3162,30 @@
         <v>0.185</v>
       </c>
       <c r="X53">
-        <v>0.912</v>
+        <v>0.91200000000000003</v>
       </c>
       <c r="Y53">
         <v>0.39</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>2002</v>
       </c>
       <c r="B54">
-        <v>9973.162</v>
+        <v>9973.1620000000003</v>
       </c>
       <c r="C54">
-        <v>147.365</v>
+        <v>147.36500000000001</v>
       </c>
       <c r="E54">
-        <v>0.194</v>
+        <v>0.19400000000000001</v>
       </c>
       <c r="F54">
-        <v>0.756</v>
+        <v>0.75600000000000001</v>
       </c>
       <c r="G54">
-        <v>0.283</v>
+        <v>0.28299999999999997</v>
       </c>
       <c r="H54">
         <v>2598</v>
@@ -3244,13 +3194,13 @@
         <v>120.309</v>
       </c>
       <c r="K54">
-        <v>0.211</v>
+        <v>0.21099999999999999</v>
       </c>
       <c r="L54">
-        <v>0.472</v>
+        <v>0.47199999999999998</v>
       </c>
       <c r="M54">
-        <v>0.904</v>
+        <v>0.90400000000000003</v>
       </c>
       <c r="N54">
         <v>765</v>
@@ -3262,28 +3212,28 @@
         <v>0.224</v>
       </c>
       <c r="R54">
-        <v>0.516</v>
+        <v>0.51600000000000001</v>
       </c>
       <c r="S54">
-        <v>0.576</v>
+        <v>0.57599999999999996</v>
       </c>
       <c r="T54">
-        <v>6610.162</v>
+        <v>6610.1620000000003</v>
       </c>
       <c r="U54">
-        <v>163.118</v>
+        <v>163.11799999999999</v>
       </c>
       <c r="W54">
-        <v>0.181</v>
+        <v>0.18099999999999999</v>
       </c>
       <c r="X54">
-        <v>0.918</v>
+        <v>0.91800000000000004</v>
       </c>
       <c r="Y54">
-        <v>0.411</v>
-      </c>
-    </row>
-    <row r="55">
+        <v>0.41099999999999998</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>2003</v>
       </c>
@@ -3294,13 +3244,13 @@
         <v>143.404</v>
       </c>
       <c r="E55">
-        <v>0.178</v>
+        <v>0.17799999999999999</v>
       </c>
       <c r="F55">
         <v>0.755</v>
       </c>
       <c r="G55">
-        <v>0.286</v>
+        <v>0.28599999999999998</v>
       </c>
       <c r="H55">
         <v>2756.59</v>
@@ -3312,10 +3262,10 @@
         <v>0.191</v>
       </c>
       <c r="L55">
-        <v>0.468</v>
+        <v>0.46800000000000003</v>
       </c>
       <c r="M55">
-        <v>0.802</v>
+        <v>0.80200000000000005</v>
       </c>
       <c r="N55">
         <v>1032</v>
@@ -3324,31 +3274,31 @@
         <v>128.625</v>
       </c>
       <c r="Q55">
-        <v>0.242</v>
+        <v>0.24199999999999999</v>
       </c>
       <c r="R55">
-        <v>0.617</v>
+        <v>0.61699999999999999</v>
       </c>
       <c r="S55">
-        <v>0.781</v>
+        <v>0.78100000000000003</v>
       </c>
       <c r="T55">
         <v>7917.82</v>
       </c>
       <c r="U55">
-        <v>155.942</v>
+        <v>155.94200000000001</v>
       </c>
       <c r="W55">
         <v>0.16</v>
       </c>
       <c r="X55">
-        <v>0.897</v>
+        <v>0.89700000000000002</v>
       </c>
       <c r="Y55">
         <v>0.42</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>2004</v>
       </c>
@@ -3356,31 +3306,31 @@
         <v>12070.5</v>
       </c>
       <c r="C56">
-        <v>149.689</v>
+        <v>149.68899999999999</v>
       </c>
       <c r="E56">
-        <v>0.173</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="F56">
-        <v>0.794</v>
+        <v>0.79400000000000004</v>
       </c>
       <c r="G56">
-        <v>0.302</v>
+        <v>0.30199999999999999</v>
       </c>
       <c r="H56">
-        <v>2590.68</v>
+        <v>2590.6799999999998</v>
       </c>
       <c r="I56">
-        <v>121.728</v>
+        <v>121.72799999999999</v>
       </c>
       <c r="K56">
         <v>0.186</v>
       </c>
       <c r="L56">
-        <v>0.468</v>
+        <v>0.46800000000000003</v>
       </c>
       <c r="M56">
-        <v>0.823</v>
+        <v>0.82299999999999995</v>
       </c>
       <c r="N56">
         <v>1319</v>
@@ -3401,19 +3351,19 @@
         <v>8160.82</v>
       </c>
       <c r="U56">
-        <v>161.069</v>
+        <v>161.06899999999999</v>
       </c>
       <c r="W56">
         <v>0.16</v>
       </c>
       <c r="X56">
-        <v>0.912</v>
+        <v>0.91200000000000003</v>
       </c>
       <c r="Y56">
-        <v>0.337</v>
-      </c>
-    </row>
-    <row r="57">
+        <v>0.33700000000000002</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>2005</v>
       </c>
@@ -3424,13 +3374,13 @@
         <v>146.917</v>
       </c>
       <c r="E57">
-        <v>0.178</v>
+        <v>0.17799999999999999</v>
       </c>
       <c r="F57">
-        <v>0.756</v>
+        <v>0.75600000000000001</v>
       </c>
       <c r="G57">
-        <v>0.323</v>
+        <v>0.32300000000000001</v>
       </c>
       <c r="H57">
         <v>2272.86</v>
@@ -3442,7 +3392,7 @@
         <v>0.184</v>
       </c>
       <c r="L57">
-        <v>0.455</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="M57">
         <v>1.36</v>
@@ -3457,28 +3407,28 @@
         <v>0.249</v>
       </c>
       <c r="R57">
-        <v>0.619</v>
+        <v>0.61899999999999999</v>
       </c>
       <c r="S57">
         <v>1.038</v>
       </c>
       <c r="T57">
-        <v>9207.736000000001</v>
+        <v>9207.7360000000008</v>
       </c>
       <c r="U57">
-        <v>158.169</v>
+        <v>158.16900000000001</v>
       </c>
       <c r="W57">
-        <v>0.165</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="X57">
         <v>0.878</v>
       </c>
       <c r="Y57">
-        <v>0.277</v>
-      </c>
-    </row>
-    <row r="58">
+        <v>0.27700000000000002</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>2006</v>
       </c>
@@ -3492,10 +3442,10 @@
         <v>0.18</v>
       </c>
       <c r="F58">
-        <v>0.761</v>
+        <v>0.76100000000000001</v>
       </c>
       <c r="G58">
-        <v>0.336</v>
+        <v>0.33600000000000002</v>
       </c>
       <c r="H58">
         <v>1960.7</v>
@@ -3504,63 +3454,63 @@
         <v>120.761</v>
       </c>
       <c r="K58">
-        <v>0.195</v>
+        <v>0.19500000000000001</v>
       </c>
       <c r="L58">
-        <v>0.457</v>
+        <v>0.45700000000000002</v>
       </c>
       <c r="M58">
-        <v>1.086</v>
+        <v>1.0860000000000001</v>
       </c>
       <c r="N58">
         <v>949</v>
       </c>
       <c r="O58">
-        <v>131.069</v>
+        <v>131.06899999999999</v>
       </c>
       <c r="Q58">
-        <v>0.232</v>
+        <v>0.23200000000000001</v>
       </c>
       <c r="R58">
-        <v>0.639</v>
+        <v>0.63900000000000001</v>
       </c>
       <c r="S58">
-        <v>0.906</v>
+        <v>0.90600000000000003</v>
       </c>
       <c r="T58">
-        <v>8619.441000000001</v>
+        <v>8619.4410000000007</v>
       </c>
       <c r="U58">
         <v>158.791</v>
       </c>
       <c r="W58">
-        <v>0.166</v>
+        <v>0.16600000000000001</v>
       </c>
       <c r="X58">
-        <v>0.882</v>
+        <v>0.88200000000000001</v>
       </c>
       <c r="Y58">
-        <v>0.259</v>
-      </c>
-    </row>
-    <row r="59">
+        <v>0.25900000000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>2007</v>
       </c>
       <c r="B59">
-        <v>12305.566</v>
+        <v>12305.566000000001</v>
       </c>
       <c r="C59">
         <v>145.196</v>
       </c>
       <c r="E59">
-        <v>0.181</v>
+        <v>0.18099999999999999</v>
       </c>
       <c r="F59">
-        <v>0.742</v>
+        <v>0.74199999999999999</v>
       </c>
       <c r="G59">
-        <v>0.342</v>
+        <v>0.34200000000000003</v>
       </c>
       <c r="H59">
         <v>2473.9</v>
@@ -3569,10 +3519,10 @@
         <v>117.621</v>
       </c>
       <c r="K59">
-        <v>0.205</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="L59">
-        <v>0.449</v>
+        <v>0.44900000000000001</v>
       </c>
       <c r="M59">
         <v>1.36</v>
@@ -3590,42 +3540,42 @@
         <v>0.6</v>
       </c>
       <c r="S59">
-        <v>1.039</v>
+        <v>1.0389999999999999</v>
       </c>
       <c r="T59">
-        <v>9053.665999999999</v>
+        <v>9053.6659999999993</v>
       </c>
       <c r="U59">
         <v>157.15</v>
       </c>
       <c r="W59">
-        <v>0.166</v>
+        <v>0.16600000000000001</v>
       </c>
       <c r="X59">
-        <v>0.864</v>
+        <v>0.86399999999999999</v>
       </c>
       <c r="Y59">
-        <v>0.331</v>
-      </c>
-    </row>
-    <row r="60">
+        <v>0.33100000000000002</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>2008</v>
       </c>
       <c r="B60">
-        <v>11102.888</v>
+        <v>11102.888000000001</v>
       </c>
       <c r="C60">
         <v>147.315</v>
       </c>
       <c r="E60">
-        <v>0.179</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="F60">
-        <v>0.776</v>
+        <v>0.77600000000000002</v>
       </c>
       <c r="G60">
-        <v>0.338</v>
+        <v>0.33800000000000002</v>
       </c>
       <c r="H60">
         <v>2404.66</v>
@@ -3634,10 +3584,10 @@
         <v>118.889</v>
       </c>
       <c r="K60">
-        <v>0.205</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="L60">
-        <v>0.455</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="M60">
         <v>1.228</v>
@@ -3646,39 +3596,39 @@
         <v>747</v>
       </c>
       <c r="O60">
-        <v>131.156</v>
+        <v>131.15600000000001</v>
       </c>
       <c r="Q60">
         <v>0.22</v>
       </c>
       <c r="R60">
-        <v>0.649</v>
+        <v>0.64900000000000002</v>
       </c>
       <c r="S60">
         <v>1.002</v>
       </c>
       <c r="T60">
-        <v>7951.228</v>
+        <v>7951.2280000000001</v>
       </c>
       <c r="U60">
         <v>159.483</v>
       </c>
       <c r="W60">
-        <v>0.163</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="X60">
-        <v>0.904</v>
+        <v>0.90400000000000003</v>
       </c>
       <c r="Y60">
         <v>0.377</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>2009</v>
       </c>
       <c r="B61">
-        <v>12146.907</v>
+        <v>12146.906999999999</v>
       </c>
       <c r="C61">
         <v>152.369</v>
@@ -3687,10 +3637,10 @@
         <v>0.183</v>
       </c>
       <c r="F61">
-        <v>0.805</v>
+        <v>0.80500000000000005</v>
       </c>
       <c r="G61">
-        <v>0.337</v>
+        <v>0.33700000000000002</v>
       </c>
       <c r="H61">
         <v>2691.31</v>
@@ -3699,10 +3649,10 @@
         <v>123.735</v>
       </c>
       <c r="K61">
-        <v>0.211</v>
+        <v>0.21099999999999999</v>
       </c>
       <c r="L61">
-        <v>0.489</v>
+        <v>0.48899999999999999</v>
       </c>
       <c r="M61">
         <v>1.056</v>
@@ -3711,34 +3661,34 @@
         <v>898</v>
       </c>
       <c r="O61">
-        <v>130.848</v>
+        <v>130.84800000000001</v>
       </c>
       <c r="Q61">
-        <v>0.207</v>
+        <v>0.20699999999999999</v>
       </c>
       <c r="R61">
-        <v>0.671</v>
+        <v>0.67100000000000004</v>
       </c>
       <c r="S61">
-        <v>1.124</v>
+        <v>1.1240000000000001</v>
       </c>
       <c r="T61">
-        <v>8557.597</v>
+        <v>8557.5969999999998</v>
       </c>
       <c r="U61">
-        <v>168.127</v>
+        <v>168.12700000000001</v>
       </c>
       <c r="W61">
-        <v>0.166</v>
+        <v>0.16600000000000001</v>
       </c>
       <c r="X61">
-        <v>0.958</v>
+        <v>0.95799999999999996</v>
       </c>
       <c r="Y61">
-        <v>0.398</v>
-      </c>
-    </row>
-    <row r="62">
+        <v>0.39800000000000002</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>2010</v>
       </c>
@@ -3752,10 +3702,10 @@
         <v>0.182</v>
       </c>
       <c r="F62">
-        <v>0.792</v>
+        <v>0.79200000000000004</v>
       </c>
       <c r="G62">
-        <v>0.333</v>
+        <v>0.33300000000000002</v>
       </c>
       <c r="H62">
         <v>2204.29</v>
@@ -3764,46 +3714,46 @@
         <v>127.46</v>
       </c>
       <c r="K62">
-        <v>0.196</v>
+        <v>0.19600000000000001</v>
       </c>
       <c r="L62">
         <v>0.505</v>
       </c>
       <c r="M62">
-        <v>0.762</v>
+        <v>0.76200000000000001</v>
       </c>
       <c r="N62">
         <v>1054</v>
       </c>
       <c r="O62">
-        <v>130.455</v>
+        <v>130.45500000000001</v>
       </c>
       <c r="Q62">
         <v>0.218</v>
       </c>
       <c r="R62">
-        <v>0.638</v>
+        <v>0.63800000000000001</v>
       </c>
       <c r="S62">
-        <v>0.981</v>
+        <v>0.98099999999999998</v>
       </c>
       <c r="T62">
-        <v>8413.879999999999</v>
+        <v>8413.8799999999992</v>
       </c>
       <c r="U62">
-        <v>167.669</v>
+        <v>167.66900000000001</v>
       </c>
       <c r="W62">
-        <v>0.169</v>
+        <v>0.16900000000000001</v>
       </c>
       <c r="X62">
-        <v>0.9379999999999999</v>
+        <v>0.93799999999999994</v>
       </c>
       <c r="Y62">
-        <v>0.414</v>
-      </c>
-    </row>
-    <row r="63">
+        <v>0.41399999999999998</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>2011</v>
       </c>
@@ -3814,13 +3764,13 @@
         <v>151.4</v>
       </c>
       <c r="E63">
-        <v>0.175</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="F63">
         <v>0.748</v>
       </c>
       <c r="G63">
-        <v>0.342</v>
+        <v>0.34200000000000003</v>
       </c>
       <c r="H63">
         <v>2571.5</v>
@@ -3832,7 +3782,7 @@
         <v>0.185</v>
       </c>
       <c r="L63">
-        <v>0.457</v>
+        <v>0.45700000000000002</v>
       </c>
       <c r="M63">
         <v>1.056</v>
@@ -3841,7 +3791,7 @@
         <v>1202</v>
       </c>
       <c r="O63">
-        <v>131.394</v>
+        <v>131.39400000000001</v>
       </c>
       <c r="Q63">
         <v>0.222</v>
@@ -3862,18 +3812,18 @@
         <v>0.158</v>
       </c>
       <c r="X63">
-        <v>0.925</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="Y63">
-        <v>0.405</v>
-      </c>
-    </row>
-    <row r="64">
+        <v>0.40500000000000003</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>2012</v>
       </c>
       <c r="B64">
-        <v>13917.042</v>
+        <v>13917.041999999999</v>
       </c>
       <c r="C64">
         <v>150.773</v>
@@ -3882,10 +3832,10 @@
         <v>0.186</v>
       </c>
       <c r="F64">
-        <v>0.766</v>
+        <v>0.76600000000000001</v>
       </c>
       <c r="G64">
-        <v>0.356</v>
+        <v>0.35599999999999998</v>
       </c>
       <c r="H64">
         <v>3346.69</v>
@@ -3897,16 +3847,16 @@
         <v>0.218</v>
       </c>
       <c r="L64">
-        <v>0.454</v>
+        <v>0.45400000000000001</v>
       </c>
       <c r="M64">
-        <v>1.066</v>
+        <v>1.0660000000000001</v>
       </c>
       <c r="N64">
         <v>882</v>
       </c>
       <c r="O64">
-        <v>135.418</v>
+        <v>135.41800000000001</v>
       </c>
       <c r="Q64">
         <v>0.217</v>
@@ -3918,22 +3868,22 @@
         <v>1.079</v>
       </c>
       <c r="T64">
-        <v>9688.352000000001</v>
+        <v>9688.3520000000008</v>
       </c>
       <c r="U64">
-        <v>167.871</v>
+        <v>167.87100000000001</v>
       </c>
       <c r="W64">
-        <v>0.163</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="X64">
-        <v>0.9370000000000001</v>
+        <v>0.93700000000000006</v>
       </c>
       <c r="Y64">
-        <v>0.448</v>
-      </c>
-    </row>
-    <row r="65">
+        <v>0.44800000000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>2013</v>
       </c>
@@ -3941,13 +3891,13 @@
         <v>12078.364</v>
       </c>
       <c r="C65">
-        <v>149.229</v>
+        <v>149.22900000000001</v>
       </c>
       <c r="E65">
-        <v>0.195</v>
+        <v>0.19500000000000001</v>
       </c>
       <c r="F65">
-        <v>0.803</v>
+        <v>0.80300000000000005</v>
       </c>
       <c r="G65">
         <v>0.378</v>
@@ -3956,7 +3906,7 @@
         <v>2812.13</v>
       </c>
       <c r="I65">
-        <v>122.016</v>
+        <v>122.01600000000001</v>
       </c>
       <c r="K65">
         <v>0.253</v>
@@ -3965,84 +3915,84 @@
         <v>0.48</v>
       </c>
       <c r="M65">
-        <v>0.9340000000000001</v>
+        <v>0.93400000000000005</v>
       </c>
       <c r="N65">
         <v>1438</v>
       </c>
       <c r="O65">
-        <v>148.969</v>
+        <v>148.96899999999999</v>
       </c>
       <c r="Q65">
-        <v>0.233</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="R65">
-        <v>0.833</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="S65">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="T65">
-        <v>7828.234</v>
+        <v>7828.2340000000004</v>
       </c>
       <c r="U65">
         <v>160.166</v>
       </c>
       <c r="W65">
-        <v>0.164</v>
+        <v>0.16400000000000001</v>
       </c>
       <c r="X65">
-        <v>0.925</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="Y65">
-        <v>0.297</v>
-      </c>
-    </row>
-    <row r="66">
+        <v>0.29699999999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>2014</v>
       </c>
       <c r="B66">
-        <v>10714.852</v>
+        <v>10714.852000000001</v>
       </c>
       <c r="C66">
         <v>151.488</v>
       </c>
       <c r="E66">
-        <v>0.181</v>
+        <v>0.18099999999999999</v>
       </c>
       <c r="F66">
-        <v>0.792</v>
+        <v>0.79200000000000004</v>
       </c>
       <c r="G66">
-        <v>0.394</v>
+        <v>0.39400000000000002</v>
       </c>
       <c r="H66">
         <v>1816.16</v>
       </c>
       <c r="I66">
-        <v>120.442</v>
+        <v>120.44199999999999</v>
       </c>
       <c r="K66">
-        <v>0.205</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="L66">
         <v>0.43</v>
       </c>
       <c r="M66">
-        <v>0.741</v>
+        <v>0.74099999999999999</v>
       </c>
       <c r="N66">
         <v>1241</v>
       </c>
       <c r="O66">
-        <v>142.263</v>
+        <v>142.26300000000001</v>
       </c>
       <c r="Q66">
         <v>0.216</v>
       </c>
       <c r="R66">
-        <v>0.783</v>
+        <v>0.78300000000000003</v>
       </c>
       <c r="S66">
         <v>0.996</v>
@@ -4054,16 +4004,16 @@
         <v>165.751</v>
       </c>
       <c r="W66">
-        <v>0.164</v>
+        <v>0.16400000000000001</v>
       </c>
       <c r="X66">
-        <v>0.9389999999999999</v>
+        <v>0.93899999999999995</v>
       </c>
       <c r="Y66">
         <v>0.35</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>2015</v>
       </c>
@@ -4080,7 +4030,7 @@
         <v>0.8</v>
       </c>
       <c r="G67">
-        <v>0.397</v>
+        <v>0.39700000000000002</v>
       </c>
       <c r="H67">
         <v>1592.8</v>
@@ -4092,16 +4042,16 @@
         <v>0.216</v>
       </c>
       <c r="L67">
-        <v>0.408</v>
+        <v>0.40799999999999997</v>
       </c>
       <c r="M67">
-        <v>0.762</v>
+        <v>0.76200000000000001</v>
       </c>
       <c r="N67">
         <v>1420</v>
       </c>
       <c r="O67">
-        <v>158.991</v>
+        <v>158.99100000000001</v>
       </c>
       <c r="Q67">
         <v>0.214</v>
@@ -4110,25 +4060,25 @@
         <v>0.875</v>
       </c>
       <c r="S67">
-        <v>0.992</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="T67">
         <v>7757.424</v>
       </c>
       <c r="U67">
-        <v>168.199</v>
+        <v>168.19900000000001</v>
       </c>
       <c r="W67">
-        <v>0.172</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="X67">
-        <v>0.9419999999999999</v>
+        <v>0.94199999999999995</v>
       </c>
       <c r="Y67">
-        <v>0.334</v>
-      </c>
-    </row>
-    <row r="68">
+        <v>0.33400000000000002</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>2016</v>
       </c>
@@ -4136,16 +4086,16 @@
         <v>10505.394</v>
       </c>
       <c r="C68">
-        <v>155.992</v>
+        <v>155.99199999999999</v>
       </c>
       <c r="E68">
         <v>0.189</v>
       </c>
       <c r="F68">
-        <v>0.8129999999999999</v>
+        <v>0.81299999999999994</v>
       </c>
       <c r="G68">
-        <v>0.402</v>
+        <v>0.40200000000000002</v>
       </c>
       <c r="H68">
         <v>1388.6</v>
@@ -4157,43 +4107,43 @@
         <v>0.224</v>
       </c>
       <c r="L68">
-        <v>0.429</v>
+        <v>0.42899999999999999</v>
       </c>
       <c r="M68">
-        <v>0.772</v>
+        <v>0.77200000000000002</v>
       </c>
       <c r="N68">
         <v>1459</v>
       </c>
       <c r="O68">
-        <v>155.163</v>
+        <v>155.16300000000001</v>
       </c>
       <c r="Q68">
-        <v>0.232</v>
+        <v>0.23200000000000001</v>
       </c>
       <c r="R68">
-        <v>0.847</v>
+        <v>0.84699999999999998</v>
       </c>
       <c r="S68">
-        <v>1.102</v>
+        <v>1.1020000000000001</v>
       </c>
       <c r="T68">
-        <v>7657.794</v>
+        <v>7657.7939999999999</v>
       </c>
       <c r="U68">
-        <v>170.855</v>
+        <v>170.85499999999999</v>
       </c>
       <c r="W68">
-        <v>0.167</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="X68">
         <v>0.96</v>
       </c>
       <c r="Y68">
-        <v>0.019</v>
-      </c>
-    </row>
-    <row r="69">
+        <v>1.9E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>2017</v>
       </c>
@@ -4204,10 +4154,10 @@
         <v>157.958</v>
       </c>
       <c r="E69">
-        <v>0.199</v>
+        <v>0.19900000000000001</v>
       </c>
       <c r="F69">
-        <v>0.798</v>
+        <v>0.79800000000000004</v>
       </c>
       <c r="G69">
         <v>0.41</v>
@@ -4219,28 +4169,28 @@
         <v>118.267</v>
       </c>
       <c r="K69">
-        <v>0.233</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="L69">
-        <v>0.422</v>
+        <v>0.42199999999999999</v>
       </c>
       <c r="M69">
-        <v>0.802</v>
+        <v>0.80200000000000005</v>
       </c>
       <c r="N69">
         <v>1871</v>
       </c>
       <c r="O69">
-        <v>153.284</v>
+        <v>153.28399999999999</v>
       </c>
       <c r="Q69">
-        <v>0.235</v>
+        <v>0.23499999999999999</v>
       </c>
       <c r="R69">
-        <v>0.831</v>
+        <v>0.83099999999999996</v>
       </c>
       <c r="S69">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="T69">
         <v>7139.98</v>
@@ -4249,21 +4199,21 @@
         <v>174.77</v>
       </c>
       <c r="W69">
-        <v>0.178</v>
+        <v>0.17799999999999999</v>
       </c>
       <c r="X69">
-        <v>0.9419999999999999</v>
+        <v>0.94199999999999995</v>
       </c>
       <c r="Y69">
-        <v>0.019</v>
-      </c>
-    </row>
-    <row r="70">
+        <v>1.9E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>2018</v>
       </c>
       <c r="B70">
-        <v>9032.781999999999</v>
+        <v>9032.7819999999992</v>
       </c>
       <c r="C70">
         <v>151.703</v>
@@ -4272,58 +4222,58 @@
         <v>0.187</v>
       </c>
       <c r="F70">
-        <v>0.767</v>
+        <v>0.76700000000000002</v>
       </c>
       <c r="G70">
-        <v>0.416</v>
+        <v>0.41599999999999998</v>
       </c>
       <c r="H70">
         <v>1105.72</v>
       </c>
       <c r="I70">
-        <v>115.564</v>
+        <v>115.56399999999999</v>
       </c>
       <c r="K70">
-        <v>0.194</v>
+        <v>0.19400000000000001</v>
       </c>
       <c r="L70">
-        <v>0.356</v>
+        <v>0.35599999999999998</v>
       </c>
       <c r="M70">
-        <v>0.975</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="N70">
         <v>1670</v>
       </c>
       <c r="O70">
-        <v>145.951</v>
+        <v>145.95099999999999</v>
       </c>
       <c r="Q70">
         <v>0.219</v>
       </c>
       <c r="R70">
-        <v>0.827</v>
+        <v>0.82699999999999996</v>
       </c>
       <c r="S70">
-        <v>1.104</v>
+        <v>1.1040000000000001</v>
       </c>
       <c r="T70">
-        <v>6257.062</v>
+        <v>6257.0619999999999</v>
       </c>
       <c r="U70">
         <v>167.309</v>
       </c>
       <c r="W70">
-        <v>0.178</v>
+        <v>0.17799999999999999</v>
       </c>
       <c r="X70">
-        <v>0.919</v>
+        <v>0.91900000000000004</v>
       </c>
       <c r="Y70">
-        <v>0.018</v>
-      </c>
-    </row>
-    <row r="71">
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>2019</v>
       </c>
@@ -4331,28 +4281,28 @@
         <v>10257.431</v>
       </c>
       <c r="C71">
-        <v>152.207</v>
+        <v>152.20699999999999</v>
       </c>
       <c r="E71">
-        <v>0.177</v>
+        <v>0.17699999999999999</v>
       </c>
       <c r="F71">
-        <v>0.801</v>
+        <v>0.80100000000000005</v>
       </c>
       <c r="G71">
-        <v>0.416</v>
+        <v>0.41599999999999998</v>
       </c>
       <c r="H71">
         <v>1455.95</v>
       </c>
       <c r="I71">
-        <v>120.368</v>
+        <v>120.36799999999999</v>
       </c>
       <c r="K71">
         <v>0.193</v>
       </c>
       <c r="L71">
-        <v>0.406</v>
+        <v>0.40600000000000003</v>
       </c>
       <c r="M71">
         <v>1.147</v>
@@ -4364,7 +4314,7 @@
         <v>148.749</v>
       </c>
       <c r="Q71">
-        <v>0.203</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="R71">
         <v>0.879</v>
@@ -4373,22 +4323,22 @@
         <v>1.482</v>
       </c>
       <c r="T71">
-        <v>6455.481</v>
+        <v>6455.4809999999998</v>
       </c>
       <c r="U71">
-        <v>165.635</v>
+        <v>165.63499999999999</v>
       </c>
       <c r="W71">
-        <v>0.165</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="X71">
-        <v>0.9429999999999999</v>
+        <v>0.94299999999999995</v>
       </c>
       <c r="Y71">
-        <v>0.023</v>
-      </c>
-    </row>
-    <row r="72">
+        <v>2.3E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>2020</v>
       </c>
@@ -4399,13 +4349,13 @@
         <v>150.922</v>
       </c>
       <c r="E72">
-        <v>0.173</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="F72">
-        <v>0.793</v>
+        <v>0.79300000000000004</v>
       </c>
       <c r="G72">
-        <v>0.412</v>
+        <v>0.41199999999999998</v>
       </c>
       <c r="H72">
         <v>1150.04</v>
@@ -4426,31 +4376,31 @@
         <v>2044</v>
       </c>
       <c r="O72">
-        <v>145.967</v>
+        <v>145.96700000000001</v>
       </c>
       <c r="Q72">
-        <v>0.204</v>
+        <v>0.20399999999999999</v>
       </c>
       <c r="R72">
-        <v>0.8159999999999999</v>
+        <v>0.81599999999999995</v>
       </c>
       <c r="S72">
         <v>1.44</v>
       </c>
       <c r="T72">
-        <v>7302.255</v>
+        <v>7302.2550000000001</v>
       </c>
       <c r="U72">
-        <v>163.621</v>
+        <v>163.62100000000001</v>
       </c>
       <c r="W72">
-        <v>0.163</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="X72">
-        <v>0.928</v>
+        <v>0.92800000000000005</v>
       </c>
       <c r="Y72">
-        <v>0.022</v>
+        <v>2.1999999999999999E-2</v>
       </c>
     </row>
   </sheetData>

--- a/Indicator_4/Real_data/Swordfish_NAtl.xlsx
+++ b/Indicator_4/Real_data/Swordfish_NAtl.xlsx
@@ -1,300 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\EcoTest_Train\Indicator_4\Real_data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C82BE9E0-4D0D-4B73-AA24-C4E9DA65F655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
     <sheet name="Time_series" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="89">
-  <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Component</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Swordfish_NAtl</t>
-  </si>
-  <si>
-    <t>E.g. 'Swordfish_Natl'</t>
-  </si>
-  <si>
-    <t>Stock</t>
-  </si>
-  <si>
-    <t>max_age</t>
-  </si>
-  <si>
-    <t>14.979</t>
-  </si>
-  <si>
-    <t>Age to 5% natural survival</t>
-  </si>
-  <si>
-    <t>Life history</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>0.093</t>
-  </si>
-  <si>
-    <t>von Bertalannfy K</t>
-  </si>
-  <si>
-    <t>Linf</t>
-  </si>
-  <si>
-    <t>0.373</t>
-  </si>
-  <si>
-    <t>von Bertalannfy L-infinity (asymptotic length)</t>
-  </si>
-  <si>
-    <t>L50_Linf</t>
-  </si>
-  <si>
-    <t>312.27</t>
-  </si>
-  <si>
-    <t>Length at 50% maturity relative to asymptotic length (von B. L-infinity)</t>
-  </si>
-  <si>
-    <t>Total_L5_L50</t>
-  </si>
-  <si>
-    <t>0.56</t>
-  </si>
-  <si>
-    <t>Length at 5% selection relative to length at 50% maturity</t>
-  </si>
-  <si>
-    <t>Fleet selectivity</t>
-  </si>
-  <si>
-    <t>All fleets combined</t>
-  </si>
-  <si>
-    <t>Total_LFS_L50</t>
-  </si>
-  <si>
-    <t>0.964</t>
-  </si>
-  <si>
-    <t>Length at full selection relative to length at 50% maturity</t>
-  </si>
-  <si>
-    <t>Total_VML</t>
-  </si>
-  <si>
-    <t>0.359</t>
-  </si>
-  <si>
-    <t>Selectivity of maximum length class</t>
-  </si>
-  <si>
-    <t>Fleet_1_L5_L50</t>
-  </si>
-  <si>
-    <t>0.501</t>
-  </si>
-  <si>
-    <t>Fleet 1</t>
-  </si>
-  <si>
-    <t>Fleet_1_LFS_L50</t>
-  </si>
-  <si>
-    <t>0.732</t>
-  </si>
-  <si>
-    <t>Fleet_1_VML</t>
-  </si>
-  <si>
-    <t>0.215</t>
-  </si>
-  <si>
-    <t>Fleet_2_L5_L50</t>
-  </si>
-  <si>
-    <t>0.625</t>
-  </si>
-  <si>
-    <t>Fleet 2</t>
-  </si>
-  <si>
-    <t>Fleet_2_LFS_L50</t>
-  </si>
-  <si>
-    <t>0.719</t>
-  </si>
-  <si>
-    <t>Fleet_2_VML</t>
-  </si>
-  <si>
-    <t>0.07</t>
-  </si>
-  <si>
-    <t>Fleet_3_L5_L50</t>
-  </si>
-  <si>
-    <t>0.585</t>
-  </si>
-  <si>
-    <t>Fleet 3</t>
-  </si>
-  <si>
-    <t>Fleet_3_LFS_L50</t>
-  </si>
-  <si>
-    <t>1.15</t>
-  </si>
-  <si>
-    <t>Fleet_3_VML</t>
-  </si>
-  <si>
-    <t>0.435</t>
-  </si>
-  <si>
-    <t>Fleet_1_CF</t>
-  </si>
-  <si>
-    <t>0.209</t>
-  </si>
-  <si>
-    <t>Fraction of all historical catches that were Fleet 1</t>
-  </si>
-  <si>
-    <t>Fleet catch scale</t>
-  </si>
-  <si>
-    <t>Fleet_2_CF</t>
-  </si>
-  <si>
-    <t>0.053</t>
-  </si>
-  <si>
-    <t>Fraction of all historical catches that were Fleet 2</t>
-  </si>
-  <si>
-    <t>Fleet_3_CF</t>
-  </si>
-  <si>
-    <t>0.738</t>
-  </si>
-  <si>
-    <t>Fraction of all historical catches that were Fleet 3</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Total_catch</t>
-  </si>
-  <si>
-    <t>Total_mean_len</t>
-  </si>
-  <si>
-    <t>Total_mean_age</t>
-  </si>
-  <si>
-    <t>Total_CV_len</t>
-  </si>
-  <si>
-    <t>Total_frac_mat</t>
-  </si>
-  <si>
-    <t>Total_Index</t>
-  </si>
-  <si>
-    <t>Fleet_1_catch</t>
-  </si>
-  <si>
-    <t>Fleet_1_mean_len</t>
-  </si>
-  <si>
-    <t>Fleet_1_mean_age</t>
-  </si>
-  <si>
-    <t>Fleet_1_CV_len</t>
-  </si>
-  <si>
-    <t>Fleet_1_frac_mat</t>
-  </si>
-  <si>
-    <t>Fleet_1_Index</t>
-  </si>
-  <si>
-    <t>Fleet_2_catch</t>
-  </si>
-  <si>
-    <t>Fleet_2_mean_len</t>
-  </si>
-  <si>
-    <t>Fleet_2_mean_age</t>
-  </si>
-  <si>
-    <t>Fleet_2_CV_len</t>
-  </si>
-  <si>
-    <t>Fleet_2_frac_mat</t>
-  </si>
-  <si>
-    <t>Fleet_2_Index</t>
-  </si>
-  <si>
-    <t>Fleet_3_catch</t>
-  </si>
-  <si>
-    <t>Fleet_3_mean_len</t>
-  </si>
-  <si>
-    <t>Fleet_3_mean_age</t>
-  </si>
-  <si>
-    <t>Fleet_3_CV_len</t>
-  </si>
-  <si>
-    <t>Fleet_3_frac_mat</t>
-  </si>
-  <si>
-    <t>Fleet_3_Index</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -342,21 +64,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -394,7 +108,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -428,7 +142,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -463,10 +176,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -639,368 +351,575 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.54296875" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" t="s">
-        <v>57</v>
-      </c>
-      <c r="E19" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" t="s">
-        <v>57</v>
-      </c>
-      <c r="E20" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>61</v>
-      </c>
-      <c r="B21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" t="s">
-        <v>63</v>
-      </c>
-      <c r="D21" t="s">
-        <v>57</v>
-      </c>
-      <c r="E21" t="s">
-        <v>49</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Swordfish_NAtl</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>E.g. 'Swordfish_Natl'</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>max_age</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>14.979</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Age to 5% natural survival</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.093</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>von Bertalannfy K</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Linf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.373</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>von Bertalannfy L-infinity (asymptotic length)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>L50_Linf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>312.27</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Length at 50% maturity relative to asymptotic length (von B. L-infinity)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Total_L5_L50</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>All fleets combined</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Total_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.964</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>All fleets combined</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Total_VML</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.359</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>All fleets combined</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Fleet_1_L5_L50</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.501</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Fleet_1_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.732</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Fleet_1_VML</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.215</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Fleet_2_L5_L50</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.625</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fleet_2_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0.719</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Fleet_2_VML</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fleet_3_L5_L50</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.585</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Fleet_3_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Fleet_3_VML</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.435</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fleet_1_CF</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.209</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Fraction of all historical catches that were Fleet 1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Fleet catch scale</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fleet_2_CF</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.053</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Fraction of all historical catches that were Fleet 2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Fleet catch scale</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Fleet_3_CF</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.738</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Fraction of all historical catches that were Fleet 3</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Fleet catch scale</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1009,88 +928,138 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Y72"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Total_catch</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Total_mean_len</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Total_mean_age</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Total_CV_len</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Total_frac_mat</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Total_Index</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_catch</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_mean_len</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_mean_age</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_CV_len</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_frac_mat</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_Index</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_catch</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_mean_len</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_mean_age</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_CV_len</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_frac_mat</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_Index</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_catch</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_mean_len</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_mean_age</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_CV_len</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_frac_mat</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_Index</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1950</v>
       </c>
@@ -1110,7 +1079,7 @@
         <v>3646</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3">
         <v>1951</v>
       </c>
@@ -1130,7 +1099,7 @@
         <v>2581</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4">
         <v>1952</v>
       </c>
@@ -1150,7 +1119,7 @@
         <v>2993</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5">
         <v>1953</v>
       </c>
@@ -1158,7 +1127,7 @@
         <v>3303</v>
       </c>
       <c r="G5">
-        <v>1.8819999999999999</v>
+        <v>1.882</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1170,7 +1139,7 @@
         <v>3303</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6">
         <v>1954</v>
       </c>
@@ -1190,7 +1159,7 @@
         <v>3034</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7">
         <v>1955</v>
       </c>
@@ -1210,7 +1179,7 @@
         <v>3502</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8">
         <v>1956</v>
       </c>
@@ -1218,7 +1187,7 @@
         <v>3358</v>
       </c>
       <c r="G8">
-        <v>1.8180000000000001</v>
+        <v>1.818</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1230,7 +1199,7 @@
         <v>3358</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9">
         <v>1957</v>
       </c>
@@ -1250,7 +1219,7 @@
         <v>4578</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10">
         <v>1958</v>
       </c>
@@ -1270,7 +1239,7 @@
         <v>4904</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11">
         <v>1959</v>
       </c>
@@ -1290,7 +1259,7 @@
         <v>6232</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12">
         <v>1960</v>
       </c>
@@ -1298,7 +1267,7 @@
         <v>3828</v>
       </c>
       <c r="G12">
-        <v>1.7310000000000001</v>
+        <v>1.731</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1310,7 +1279,7 @@
         <v>3828</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="13">
       <c r="A13">
         <v>1961</v>
       </c>
@@ -1330,7 +1299,7 @@
         <v>4381</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14">
         <v>1962</v>
       </c>
@@ -1338,7 +1307,7 @@
         <v>5342</v>
       </c>
       <c r="G14">
-        <v>1.6739999999999999</v>
+        <v>1.674</v>
       </c>
       <c r="H14">
         <v>65</v>
@@ -1350,10 +1319,10 @@
         <v>5277</v>
       </c>
       <c r="Y14">
-        <v>2.5999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.026</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15">
         <v>1963</v>
       </c>
@@ -1361,7 +1330,7 @@
         <v>10190</v>
       </c>
       <c r="G15">
-        <v>1.6639999999999999</v>
+        <v>1.664</v>
       </c>
       <c r="H15">
         <v>1053</v>
@@ -1373,10 +1342,10 @@
         <v>9137</v>
       </c>
       <c r="Y15">
-        <v>11.332000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+        <v>11.332</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16">
         <v>1964</v>
       </c>
@@ -1396,10 +1365,10 @@
         <v>9979</v>
       </c>
       <c r="Y16">
-        <v>3.9860000000000002</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+        <v>3.986</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17">
         <v>1965</v>
       </c>
@@ -1407,7 +1376,7 @@
         <v>8652</v>
       </c>
       <c r="G17">
-        <v>1.6379999999999999</v>
+        <v>1.638</v>
       </c>
       <c r="H17">
         <v>945</v>
@@ -1419,10 +1388,10 @@
         <v>7707</v>
       </c>
       <c r="Y17">
-        <v>2.4609999999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
+        <v>2.461</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18">
         <v>1966</v>
       </c>
@@ -1430,7 +1399,7 @@
         <v>9349</v>
       </c>
       <c r="G18">
-        <v>1.5840000000000001</v>
+        <v>1.584</v>
       </c>
       <c r="H18">
         <v>534</v>
@@ -1442,10 +1411,10 @@
         <v>8815</v>
       </c>
       <c r="Y18">
-        <v>2.4849999999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
+        <v>2.485</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19">
         <v>1967</v>
       </c>
@@ -1465,10 +1434,10 @@
         <v>8767</v>
       </c>
       <c r="Y19">
-        <v>2.9140000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+        <v>2.914</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20">
         <v>1968</v>
       </c>
@@ -1491,7 +1460,7 @@
         <v>1.556</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="21">
       <c r="A21">
         <v>1969</v>
       </c>
@@ -1514,7 +1483,7 @@
         <v>1.421</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="22">
       <c r="A22">
         <v>1970</v>
       </c>
@@ -1522,25 +1491,25 @@
         <v>9578</v>
       </c>
       <c r="C22">
-        <v>154.76400000000001</v>
+        <v>154.764</v>
       </c>
       <c r="E22">
-        <v>0.19600000000000001</v>
+        <v>0.196</v>
       </c>
       <c r="F22">
         <v>0.876</v>
       </c>
       <c r="G22">
-        <v>1.4139999999999999</v>
+        <v>1.414</v>
       </c>
       <c r="H22">
         <v>287</v>
       </c>
       <c r="I22">
-        <v>154.76400000000001</v>
+        <v>154.764</v>
       </c>
       <c r="K22">
-        <v>0.19600000000000001</v>
+        <v>0.196</v>
       </c>
       <c r="L22">
         <v>0.876</v>
@@ -1552,10 +1521,10 @@
         <v>9291</v>
       </c>
       <c r="Y22">
-        <v>1.6120000000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.612</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23">
         <v>1971</v>
       </c>
@@ -1563,13 +1532,13 @@
         <v>5266</v>
       </c>
       <c r="C23">
-        <v>140.00899999999999</v>
+        <v>140.009</v>
       </c>
       <c r="E23">
-        <v>0.28799999999999998</v>
+        <v>0.288</v>
       </c>
       <c r="F23">
-        <v>0.70399999999999996</v>
+        <v>0.704</v>
       </c>
       <c r="G23">
         <v>1.381</v>
@@ -1584,19 +1553,19 @@
         <v>5231</v>
       </c>
       <c r="U23">
-        <v>140.00899999999999</v>
+        <v>140.009</v>
       </c>
       <c r="W23">
-        <v>0.28799999999999998</v>
+        <v>0.288</v>
       </c>
       <c r="X23">
-        <v>0.70399999999999996</v>
+        <v>0.704</v>
       </c>
       <c r="Y23">
-        <v>3.4000000000000002E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.034</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24">
         <v>1972</v>
       </c>
@@ -1604,13 +1573,13 @@
         <v>4766</v>
       </c>
       <c r="C24">
-        <v>161.02000000000001</v>
+        <v>161.02</v>
       </c>
       <c r="E24">
         <v>0.22</v>
       </c>
       <c r="F24">
-        <v>0.88800000000000001</v>
+        <v>0.888</v>
       </c>
       <c r="G24">
         <v>1.351</v>
@@ -1625,19 +1594,19 @@
         <v>4520</v>
       </c>
       <c r="U24">
-        <v>161.02000000000001</v>
+        <v>161.02</v>
       </c>
       <c r="W24">
         <v>0.22</v>
       </c>
       <c r="X24">
-        <v>0.88800000000000001</v>
+        <v>0.888</v>
       </c>
       <c r="Y24">
-        <v>3.2000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.032</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25">
         <v>1973</v>
       </c>
@@ -1657,10 +1626,10 @@
         <v>5668</v>
       </c>
       <c r="Y25">
-        <v>3.4000000000000002E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.034</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26">
         <v>1974</v>
       </c>
@@ -1668,28 +1637,28 @@
         <v>6362</v>
       </c>
       <c r="C26">
-        <v>143.76499999999999</v>
+        <v>143.765</v>
       </c>
       <c r="E26">
-        <v>0.23400000000000001</v>
+        <v>0.234</v>
       </c>
       <c r="F26">
-        <v>0.73299999999999998</v>
+        <v>0.733</v>
       </c>
       <c r="G26">
-        <v>1.3240000000000001</v>
+        <v>1.324</v>
       </c>
       <c r="H26">
         <v>1125</v>
       </c>
       <c r="I26">
-        <v>143.76499999999999</v>
+        <v>143.765</v>
       </c>
       <c r="K26">
-        <v>0.23400000000000001</v>
+        <v>0.234</v>
       </c>
       <c r="L26">
-        <v>0.73299999999999998</v>
+        <v>0.733</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -1698,10 +1667,10 @@
         <v>5237</v>
       </c>
       <c r="Y26">
-        <v>3.2000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.032</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27">
         <v>1975</v>
       </c>
@@ -1715,7 +1684,7 @@
         <v>0.222</v>
       </c>
       <c r="F27">
-        <v>0.89600000000000002</v>
+        <v>0.896</v>
       </c>
       <c r="G27">
         <v>1.333</v>
@@ -1724,13 +1693,13 @@
         <v>1700</v>
       </c>
       <c r="I27">
-        <v>150.61699999999999</v>
+        <v>150.617</v>
       </c>
       <c r="K27">
         <v>0.218</v>
       </c>
       <c r="L27">
-        <v>0.82699999999999996</v>
+        <v>0.827</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -1739,19 +1708,19 @@
         <v>7139</v>
       </c>
       <c r="U27">
-        <v>193.40700000000001</v>
+        <v>193.407</v>
       </c>
       <c r="W27">
-        <v>0.22700000000000001</v>
+        <v>0.227</v>
       </c>
       <c r="X27">
-        <v>0.96499999999999997</v>
+        <v>0.965</v>
       </c>
       <c r="Y27">
         <v>4.218</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="28">
       <c r="A28">
         <v>1976</v>
       </c>
@@ -1759,16 +1728,16 @@
         <v>6696</v>
       </c>
       <c r="C28">
-        <v>164.42099999999999</v>
+        <v>164.421</v>
       </c>
       <c r="E28">
         <v>0.219</v>
       </c>
       <c r="F28">
-        <v>0.88100000000000001</v>
+        <v>0.881</v>
       </c>
       <c r="G28">
-        <v>1.3360000000000001</v>
+        <v>1.336</v>
       </c>
       <c r="H28">
         <v>1429</v>
@@ -1780,7 +1749,7 @@
         <v>0.222</v>
       </c>
       <c r="L28">
-        <v>0.79600000000000004</v>
+        <v>0.796</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -1789,19 +1758,19 @@
         <v>5267</v>
       </c>
       <c r="U28">
-        <v>181.78100000000001</v>
+        <v>181.781</v>
       </c>
       <c r="W28">
         <v>0.217</v>
       </c>
       <c r="X28">
-        <v>0.96599999999999997</v>
+        <v>0.966</v>
       </c>
       <c r="Y28">
-        <v>2.3050000000000002</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
+        <v>2.305</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29">
         <v>1977</v>
       </c>
@@ -1809,28 +1778,28 @@
         <v>6409</v>
       </c>
       <c r="C29">
-        <v>161.97800000000001</v>
+        <v>161.978</v>
       </c>
       <c r="E29">
-        <v>0.20699999999999999</v>
+        <v>0.207</v>
       </c>
       <c r="F29">
-        <v>0.89700000000000002</v>
+        <v>0.897</v>
       </c>
       <c r="G29">
-        <v>1.3360000000000001</v>
+        <v>1.336</v>
       </c>
       <c r="H29">
         <v>912</v>
       </c>
       <c r="I29">
-        <v>147.93899999999999</v>
+        <v>147.939</v>
       </c>
       <c r="K29">
         <v>0.222</v>
       </c>
       <c r="L29">
-        <v>0.81799999999999995</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -1839,19 +1808,19 @@
         <v>5497</v>
       </c>
       <c r="U29">
-        <v>176.01599999999999</v>
+        <v>176.016</v>
       </c>
       <c r="W29">
         <v>0.191</v>
       </c>
       <c r="X29">
-        <v>0.97599999999999998</v>
+        <v>0.976</v>
       </c>
       <c r="Y29">
-        <v>2.6619999999999999</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
+        <v>2.662</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30">
         <v>1978</v>
       </c>
@@ -1859,10 +1828,10 @@
         <v>11827</v>
       </c>
       <c r="C30">
-        <v>167.91200000000001</v>
+        <v>167.912</v>
       </c>
       <c r="E30">
-        <v>0.19900000000000001</v>
+        <v>0.199</v>
       </c>
       <c r="F30">
         <v>0.93</v>
@@ -1874,10 +1843,10 @@
         <v>3020</v>
       </c>
       <c r="I30">
-        <v>154.07599999999999</v>
+        <v>154.076</v>
       </c>
       <c r="K30">
-        <v>0.20899999999999999</v>
+        <v>0.209</v>
       </c>
       <c r="L30">
         <v>0.876</v>
@@ -1889,19 +1858,19 @@
         <v>8807</v>
       </c>
       <c r="U30">
-        <v>181.74799999999999</v>
+        <v>181.748</v>
       </c>
       <c r="W30">
         <v>0.188</v>
       </c>
       <c r="X30">
-        <v>0.98299999999999998</v>
+        <v>0.983</v>
       </c>
       <c r="Y30">
-        <v>3.0379999999999998</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
+        <v>3.038</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31">
         <v>1979</v>
       </c>
@@ -1918,19 +1887,19 @@
         <v>0.84</v>
       </c>
       <c r="G31">
-        <v>1.3169999999999999</v>
+        <v>1.317</v>
       </c>
       <c r="H31">
         <v>3888</v>
       </c>
       <c r="I31">
-        <v>149.67400000000001</v>
+        <v>149.674</v>
       </c>
       <c r="K31">
         <v>0.252</v>
       </c>
       <c r="L31">
-        <v>0.77300000000000002</v>
+        <v>0.773</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -1942,16 +1911,16 @@
         <v>168.267</v>
       </c>
       <c r="W31">
-        <v>0.22800000000000001</v>
+        <v>0.228</v>
       </c>
       <c r="X31">
-        <v>0.90700000000000003</v>
+        <v>0.907</v>
       </c>
       <c r="Y31">
         <v>1.752</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="32">
       <c r="A32">
         <v>1980</v>
       </c>
@@ -1959,22 +1928,22 @@
         <v>13558</v>
       </c>
       <c r="C32">
-        <v>170.92599999999999</v>
+        <v>170.926</v>
       </c>
       <c r="E32">
-        <v>0.20200000000000001</v>
+        <v>0.202</v>
       </c>
       <c r="F32">
-        <v>0.89600000000000002</v>
+        <v>0.896</v>
       </c>
       <c r="G32">
-        <v>1.3149999999999999</v>
+        <v>1.315</v>
       </c>
       <c r="H32">
         <v>5015</v>
       </c>
       <c r="I32">
-        <v>144.72200000000001</v>
+        <v>144.722</v>
       </c>
       <c r="K32">
         <v>0.252</v>
@@ -1989,10 +1958,10 @@
         <v>8543</v>
       </c>
       <c r="U32">
-        <v>184.02799999999999</v>
+        <v>184.028</v>
       </c>
       <c r="W32">
-        <v>0.17699999999999999</v>
+        <v>0.177</v>
       </c>
       <c r="X32">
         <v>0.97</v>
@@ -2001,7 +1970,7 @@
         <v>1.758</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="33">
       <c r="A33">
         <v>1981</v>
       </c>
@@ -2009,13 +1978,13 @@
         <v>11197</v>
       </c>
       <c r="C33">
-        <v>169.61799999999999</v>
+        <v>169.618</v>
       </c>
       <c r="E33">
         <v>0.184</v>
       </c>
       <c r="F33">
-        <v>0.93799999999999994</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="G33">
         <v>1.276</v>
@@ -2045,13 +2014,13 @@
         <v>0.16</v>
       </c>
       <c r="X33">
-        <v>0.98699999999999999</v>
+        <v>0.987</v>
       </c>
       <c r="Y33">
         <v>1.617</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="34">
       <c r="A34">
         <v>1982</v>
       </c>
@@ -2059,10 +2028,10 @@
         <v>13215</v>
       </c>
       <c r="C34">
-        <v>172.83500000000001</v>
+        <v>172.835</v>
       </c>
       <c r="E34">
-        <v>0.20599999999999999</v>
+        <v>0.206</v>
       </c>
       <c r="F34">
         <v>0.91</v>
@@ -2074,13 +2043,13 @@
         <v>5271</v>
       </c>
       <c r="I34">
-        <v>145.16800000000001</v>
+        <v>145.168</v>
       </c>
       <c r="K34">
         <v>0.26</v>
       </c>
       <c r="L34">
-        <v>0.74299999999999999</v>
+        <v>0.743</v>
       </c>
       <c r="N34">
         <v>4</v>
@@ -2089,19 +2058,19 @@
         <v>7940</v>
       </c>
       <c r="U34">
-        <v>182.05799999999999</v>
+        <v>182.058</v>
       </c>
       <c r="W34">
         <v>0.189</v>
       </c>
       <c r="X34">
-        <v>0.96599999999999997</v>
+        <v>0.966</v>
       </c>
       <c r="Y34">
-        <v>0.71099999999999997</v>
-      </c>
-    </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.711</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35">
         <v>1983</v>
       </c>
@@ -2109,16 +2078,16 @@
         <v>14563</v>
       </c>
       <c r="C35">
-        <v>169.13900000000001</v>
+        <v>169.139</v>
       </c>
       <c r="E35">
         <v>0.184</v>
       </c>
       <c r="F35">
-        <v>0.89800000000000002</v>
+        <v>0.898</v>
       </c>
       <c r="G35">
-        <v>1.1850000000000001</v>
+        <v>1.185</v>
       </c>
       <c r="H35">
         <v>4510</v>
@@ -2127,10 +2096,10 @@
         <v>142.35</v>
       </c>
       <c r="K35">
-        <v>0.27200000000000002</v>
+        <v>0.272</v>
       </c>
       <c r="L35">
-        <v>0.68600000000000005</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="N35">
         <v>3</v>
@@ -2139,19 +2108,19 @@
         <v>10050</v>
       </c>
       <c r="U35">
-        <v>178.06800000000001</v>
+        <v>178.068</v>
       </c>
       <c r="W35">
         <v>0.154</v>
       </c>
       <c r="X35">
-        <v>0.96799999999999997</v>
+        <v>0.968</v>
       </c>
       <c r="Y35">
-        <v>0.57199999999999995</v>
-      </c>
-    </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.572</v>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36">
         <v>1984</v>
       </c>
@@ -2159,13 +2128,13 @@
         <v>12833</v>
       </c>
       <c r="C36">
-        <v>148.07599999999999</v>
+        <v>148.076</v>
       </c>
       <c r="E36">
         <v>0.22</v>
       </c>
       <c r="F36">
-        <v>0.82299999999999995</v>
+        <v>0.823</v>
       </c>
       <c r="G36">
         <v>1.145</v>
@@ -2174,7 +2143,7 @@
         <v>4666</v>
       </c>
       <c r="I36">
-        <v>136.87799999999999</v>
+        <v>136.878</v>
       </c>
       <c r="K36">
         <v>0.255</v>
@@ -2192,16 +2161,16 @@
         <v>151.809</v>
       </c>
       <c r="W36">
-        <v>0.20799999999999999</v>
+        <v>0.208</v>
       </c>
       <c r="X36">
         <v>0.873</v>
       </c>
       <c r="Y36">
-        <v>0.51700000000000002</v>
-      </c>
-    </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.517</v>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37">
         <v>1985</v>
       </c>
@@ -2212,7 +2181,7 @@
         <v>149.352</v>
       </c>
       <c r="E37">
-        <v>0.20399999999999999</v>
+        <v>0.204</v>
       </c>
       <c r="F37">
         <v>0.85</v>
@@ -2224,13 +2193,13 @@
         <v>4642</v>
       </c>
       <c r="I37">
-        <v>138.01300000000001</v>
+        <v>138.013</v>
       </c>
       <c r="K37">
         <v>0.255</v>
       </c>
       <c r="L37">
-        <v>0.68600000000000005</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="N37">
         <v>15</v>
@@ -2245,13 +2214,13 @@
         <v>0.187</v>
       </c>
       <c r="X37">
-        <v>0.90500000000000003</v>
+        <v>0.905</v>
       </c>
       <c r="Y37">
         <v>0.59</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="38">
       <c r="A38">
         <v>1986</v>
       </c>
@@ -2265,7 +2234,7 @@
         <v>0.183</v>
       </c>
       <c r="F38">
-        <v>0.86699999999999999</v>
+        <v>0.867</v>
       </c>
       <c r="G38">
         <v>1.008</v>
@@ -2280,7 +2249,7 @@
         <v>0.248</v>
       </c>
       <c r="L38">
-        <v>0.65500000000000003</v>
+        <v>0.655</v>
       </c>
       <c r="N38">
         <v>448</v>
@@ -2292,16 +2261,16 @@
         <v>159.779</v>
       </c>
       <c r="W38">
-        <v>0.16700000000000001</v>
+        <v>0.167</v>
       </c>
       <c r="X38">
         <v>0.92</v>
       </c>
       <c r="Y38">
-        <v>0.51900000000000002</v>
-      </c>
-    </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.519</v>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39">
         <v>1987</v>
       </c>
@@ -2312,19 +2281,19 @@
         <v>153.011</v>
       </c>
       <c r="E39">
-        <v>0.24099999999999999</v>
+        <v>0.241</v>
       </c>
       <c r="F39">
-        <v>0.77600000000000002</v>
+        <v>0.776</v>
       </c>
       <c r="G39">
-        <v>0.93500000000000005</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="H39">
         <v>5164</v>
       </c>
       <c r="I39">
-        <v>130.56100000000001</v>
+        <v>130.561</v>
       </c>
       <c r="K39">
         <v>0.247</v>
@@ -2336,7 +2305,7 @@
         <v>984</v>
       </c>
       <c r="O39">
-        <v>143.00700000000001</v>
+        <v>143.007</v>
       </c>
       <c r="Q39">
         <v>0.255</v>
@@ -2351,16 +2320,16 @@
         <v>161.125</v>
       </c>
       <c r="W39">
-        <v>0.23599999999999999</v>
+        <v>0.236</v>
       </c>
       <c r="X39">
-        <v>0.82399999999999995</v>
+        <v>0.824</v>
       </c>
       <c r="Y39">
-        <v>0.42399999999999999</v>
-      </c>
-    </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.424</v>
+      </c>
+    </row>
+    <row r="40">
       <c r="A40">
         <v>1988</v>
       </c>
@@ -2368,16 +2337,16 @@
         <v>19525</v>
       </c>
       <c r="C40">
-        <v>153.92400000000001</v>
+        <v>153.924</v>
       </c>
       <c r="E40">
-        <v>0.20300000000000001</v>
+        <v>0.203</v>
       </c>
       <c r="F40">
-        <v>0.82099999999999995</v>
+        <v>0.821</v>
       </c>
       <c r="G40">
-        <v>0.85599999999999998</v>
+        <v>0.856</v>
       </c>
       <c r="H40">
         <v>6020</v>
@@ -2389,7 +2358,7 @@
         <v>0.247</v>
       </c>
       <c r="L40">
-        <v>0.57699999999999996</v>
+        <v>0.577</v>
       </c>
       <c r="N40">
         <v>612</v>
@@ -2398,19 +2367,19 @@
         <v>12893</v>
       </c>
       <c r="U40">
-        <v>160.66900000000001</v>
+        <v>160.669</v>
       </c>
       <c r="W40">
         <v>0.192</v>
       </c>
       <c r="X40">
-        <v>0.88200000000000001</v>
+        <v>0.882</v>
       </c>
       <c r="Y40">
         <v>0.439</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="41">
       <c r="A41">
         <v>1989</v>
       </c>
@@ -2421,25 +2390,25 @@
         <v>157.244</v>
       </c>
       <c r="E41">
-        <v>0.20100000000000001</v>
+        <v>0.201</v>
       </c>
       <c r="F41">
-        <v>0.82699999999999996</v>
+        <v>0.827</v>
       </c>
       <c r="G41">
-        <v>0.76600000000000001</v>
+        <v>0.766</v>
       </c>
       <c r="H41">
         <v>5855</v>
       </c>
       <c r="I41">
-        <v>128.36699999999999</v>
+        <v>128.367</v>
       </c>
       <c r="K41">
-        <v>0.24399999999999999</v>
+        <v>0.244</v>
       </c>
       <c r="L41">
-        <v>0.58499999999999996</v>
+        <v>0.585</v>
       </c>
       <c r="N41">
         <v>292</v>
@@ -2448,19 +2417,19 @@
         <v>11114</v>
       </c>
       <c r="U41">
-        <v>164.46299999999999</v>
+        <v>164.463</v>
       </c>
       <c r="W41">
         <v>0.19</v>
       </c>
       <c r="X41">
-        <v>0.88800000000000001</v>
+        <v>0.888</v>
       </c>
       <c r="Y41">
-        <v>0.38300000000000001</v>
-      </c>
-    </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.383</v>
+      </c>
+    </row>
+    <row r="42">
       <c r="A42">
         <v>1990</v>
       </c>
@@ -2468,16 +2437,16 @@
         <v>15672</v>
       </c>
       <c r="C42">
-        <v>154.48599999999999</v>
+        <v>154.486</v>
       </c>
       <c r="E42">
-        <v>0.17699999999999999</v>
+        <v>0.177</v>
       </c>
       <c r="F42">
         <v>0.86</v>
       </c>
       <c r="G42">
-        <v>0.68100000000000005</v>
+        <v>0.681</v>
       </c>
       <c r="H42">
         <v>4967</v>
@@ -2489,37 +2458,37 @@
         <v>0.24</v>
       </c>
       <c r="L42">
-        <v>0.63200000000000001</v>
+        <v>0.632</v>
       </c>
       <c r="N42">
         <v>463</v>
       </c>
       <c r="O42">
-        <v>131.30000000000001</v>
+        <v>131.3</v>
       </c>
       <c r="Q42">
-        <v>0.17499999999999999</v>
+        <v>0.175</v>
       </c>
       <c r="R42">
-        <v>0.70299999999999996</v>
+        <v>0.703</v>
       </c>
       <c r="T42">
         <v>10242</v>
       </c>
       <c r="U42">
-        <v>163.95500000000001</v>
+        <v>163.955</v>
       </c>
       <c r="W42">
-        <v>0.16400000000000001</v>
+        <v>0.164</v>
       </c>
       <c r="X42">
-        <v>0.93700000000000006</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="Y42">
-        <v>0.47899999999999998</v>
-      </c>
-    </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.479</v>
+      </c>
+    </row>
+    <row r="43">
       <c r="A43">
         <v>1991</v>
       </c>
@@ -2530,10 +2499,10 @@
         <v>161.392</v>
       </c>
       <c r="E43">
-        <v>0.17799999999999999</v>
+        <v>0.178</v>
       </c>
       <c r="F43">
-        <v>0.91700000000000004</v>
+        <v>0.917</v>
       </c>
       <c r="G43">
         <v>0.61</v>
@@ -2545,7 +2514,7 @@
         <v>137.023</v>
       </c>
       <c r="K43">
-        <v>0.22700000000000001</v>
+        <v>0.227</v>
       </c>
       <c r="L43">
         <v>0.746</v>
@@ -2557,19 +2526,19 @@
         <v>9778</v>
       </c>
       <c r="U43">
-        <v>166.26599999999999</v>
+        <v>166.266</v>
       </c>
       <c r="W43">
-        <v>0.16800000000000001</v>
+        <v>0.168</v>
       </c>
       <c r="X43">
-        <v>0.95099999999999996</v>
+        <v>0.951</v>
       </c>
       <c r="Y43">
-        <v>0.48099999999999998</v>
-      </c>
-    </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.481</v>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44">
         <v>1992</v>
       </c>
@@ -2580,25 +2549,25 @@
         <v>162.376</v>
       </c>
       <c r="E44">
-        <v>0.17299999999999999</v>
+        <v>0.173</v>
       </c>
       <c r="F44">
-        <v>0.92500000000000004</v>
+        <v>0.925</v>
       </c>
       <c r="G44">
-        <v>0.55500000000000005</v>
+        <v>0.555</v>
       </c>
       <c r="H44">
         <v>4124</v>
       </c>
       <c r="I44">
-        <v>145.08000000000001</v>
+        <v>145.08</v>
       </c>
       <c r="K44">
         <v>0.187</v>
       </c>
       <c r="L44">
-        <v>0.89400000000000002</v>
+        <v>0.894</v>
       </c>
       <c r="N44">
         <v>497</v>
@@ -2607,19 +2576,19 @@
         <v>10773</v>
       </c>
       <c r="U44">
-        <v>165.83500000000001</v>
+        <v>165.835</v>
       </c>
       <c r="W44">
         <v>0.17</v>
       </c>
       <c r="X44">
-        <v>0.93100000000000005</v>
+        <v>0.931</v>
       </c>
       <c r="Y44">
-        <v>0.40300000000000002</v>
-      </c>
-    </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.403</v>
+      </c>
+    </row>
+    <row r="45">
       <c r="A45">
         <v>1993</v>
       </c>
@@ -2633,10 +2602,10 @@
         <v>0.19</v>
       </c>
       <c r="F45">
-        <v>0.77300000000000002</v>
+        <v>0.773</v>
       </c>
       <c r="G45">
-        <v>0.51700000000000002</v>
+        <v>0.517</v>
       </c>
       <c r="H45">
         <v>4044</v>
@@ -2648,10 +2617,10 @@
         <v>0.189</v>
       </c>
       <c r="L45">
-        <v>0.50700000000000001</v>
+        <v>0.507</v>
       </c>
       <c r="M45">
-        <v>0.90400000000000003</v>
+        <v>0.904</v>
       </c>
       <c r="N45">
         <v>1950</v>
@@ -2663,7 +2632,7 @@
         <v>0.252</v>
       </c>
       <c r="R45">
-        <v>0.54500000000000004</v>
+        <v>0.545</v>
       </c>
       <c r="T45">
         <v>10744</v>
@@ -2672,16 +2641,16 @@
         <v>162.755</v>
       </c>
       <c r="W45">
-        <v>0.17799999999999999</v>
+        <v>0.178</v>
       </c>
       <c r="X45">
-        <v>0.92500000000000004</v>
+        <v>0.925</v>
       </c>
       <c r="Y45">
-        <v>0.39400000000000002</v>
-      </c>
-    </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.394</v>
+      </c>
+    </row>
+    <row r="46">
       <c r="A46">
         <v>1994</v>
       </c>
@@ -2692,10 +2661,10 @@
         <v>150.685</v>
       </c>
       <c r="E46">
-        <v>0.17199999999999999</v>
+        <v>0.172</v>
       </c>
       <c r="F46">
-        <v>0.78700000000000003</v>
+        <v>0.787</v>
       </c>
       <c r="G46">
         <v>0.49</v>
@@ -2707,13 +2676,13 @@
         <v>122.405</v>
       </c>
       <c r="K46">
-        <v>0.16700000000000001</v>
+        <v>0.167</v>
       </c>
       <c r="L46">
-        <v>0.51700000000000002</v>
+        <v>0.517</v>
       </c>
       <c r="M46">
-        <v>0.94399999999999995</v>
+        <v>0.944</v>
       </c>
       <c r="N46">
         <v>1579</v>
@@ -2722,28 +2691,28 @@
         <v>126.521</v>
       </c>
       <c r="Q46">
-        <v>0.17399999999999999</v>
+        <v>0.174</v>
       </c>
       <c r="R46">
-        <v>0.60399999999999998</v>
+        <v>0.604</v>
       </c>
       <c r="T46">
         <v>9962</v>
       </c>
       <c r="U46">
-        <v>166.82900000000001</v>
+        <v>166.829</v>
       </c>
       <c r="W46">
-        <v>0.17299999999999999</v>
+        <v>0.173</v>
       </c>
       <c r="X46">
-        <v>0.93100000000000005</v>
+        <v>0.931</v>
       </c>
       <c r="Y46">
-        <v>0.32700000000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.327</v>
+      </c>
+    </row>
+    <row r="47">
       <c r="A47">
         <v>1995</v>
       </c>
@@ -2751,31 +2720,31 @@
         <v>17105</v>
       </c>
       <c r="C47">
-        <v>149.24799999999999</v>
+        <v>149.248</v>
       </c>
       <c r="E47">
-        <v>0.17599999999999999</v>
+        <v>0.176</v>
       </c>
       <c r="F47">
         <v>0.8</v>
       </c>
       <c r="G47">
-        <v>0.46400000000000002</v>
+        <v>0.464</v>
       </c>
       <c r="H47">
         <v>4452</v>
       </c>
       <c r="I47">
-        <v>122.20399999999999</v>
+        <v>122.204</v>
       </c>
       <c r="K47">
-        <v>0.17899999999999999</v>
+        <v>0.179</v>
       </c>
       <c r="L47">
-        <v>0.53500000000000003</v>
+        <v>0.535</v>
       </c>
       <c r="M47">
-        <v>0.95399999999999996</v>
+        <v>0.954</v>
       </c>
       <c r="N47">
         <v>1593</v>
@@ -2784,28 +2753,28 @@
         <v>126.997</v>
       </c>
       <c r="Q47">
-        <v>0.18099999999999999</v>
+        <v>0.181</v>
       </c>
       <c r="R47">
-        <v>0.64600000000000002</v>
+        <v>0.646</v>
       </c>
       <c r="T47">
         <v>11060</v>
       </c>
       <c r="U47">
-        <v>164.51499999999999</v>
+        <v>164.515</v>
       </c>
       <c r="W47">
-        <v>0.17299999999999999</v>
+        <v>0.173</v>
       </c>
       <c r="X47">
-        <v>0.93700000000000006</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="Y47">
-        <v>0.35499999999999998</v>
-      </c>
-    </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.355</v>
+      </c>
+    </row>
+    <row r="48">
       <c r="A48">
         <v>1996</v>
       </c>
@@ -2816,13 +2785,13 @@
         <v>154.875</v>
       </c>
       <c r="E48">
-        <v>0.16300000000000001</v>
+        <v>0.163</v>
       </c>
       <c r="F48">
-        <v>0.81200000000000006</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G48">
-        <v>0.42299999999999999</v>
+        <v>0.423</v>
       </c>
       <c r="H48">
         <v>4015</v>
@@ -2846,19 +2815,19 @@
         <v>9505</v>
       </c>
       <c r="U48">
-        <v>167.61699999999999</v>
+        <v>167.617</v>
       </c>
       <c r="W48">
-        <v>0.16700000000000001</v>
+        <v>0.167</v>
       </c>
       <c r="X48">
-        <v>0.93899999999999995</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="Y48">
-        <v>0.26600000000000001</v>
-      </c>
-    </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.266</v>
+      </c>
+    </row>
+    <row r="49">
       <c r="A49">
         <v>1997</v>
       </c>
@@ -2866,31 +2835,31 @@
         <v>13025</v>
       </c>
       <c r="C49">
-        <v>153.78899999999999</v>
+        <v>153.789</v>
       </c>
       <c r="E49">
-        <v>0.17499999999999999</v>
+        <v>0.175</v>
       </c>
       <c r="F49">
-        <v>0.79200000000000004</v>
+        <v>0.792</v>
       </c>
       <c r="G49">
-        <v>0.38900000000000001</v>
+        <v>0.389</v>
       </c>
       <c r="H49">
         <v>3399</v>
       </c>
       <c r="I49">
-        <v>122.89400000000001</v>
+        <v>122.894</v>
       </c>
       <c r="K49">
-        <v>0.17299999999999999</v>
+        <v>0.173</v>
       </c>
       <c r="L49">
-        <v>0.51500000000000001</v>
+        <v>0.515</v>
       </c>
       <c r="M49">
-        <v>0.95399999999999996</v>
+        <v>0.954</v>
       </c>
       <c r="N49">
         <v>902</v>
@@ -2899,19 +2868,19 @@
         <v>8724</v>
       </c>
       <c r="U49">
-        <v>166.14699999999999</v>
+        <v>166.147</v>
       </c>
       <c r="W49">
-        <v>0.17599999999999999</v>
+        <v>0.176</v>
       </c>
       <c r="X49">
-        <v>0.90300000000000002</v>
+        <v>0.903</v>
       </c>
       <c r="Y49">
-        <v>0.27400000000000002</v>
-      </c>
-    </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.274</v>
+      </c>
+    </row>
+    <row r="50">
       <c r="A50">
         <v>1998</v>
       </c>
@@ -2922,13 +2891,13 @@
         <v>148.411</v>
       </c>
       <c r="E50">
-        <v>0.16700000000000001</v>
+        <v>0.167</v>
       </c>
       <c r="F50">
-        <v>0.77100000000000002</v>
+        <v>0.771</v>
       </c>
       <c r="G50">
-        <v>0.34899999999999998</v>
+        <v>0.349</v>
       </c>
       <c r="H50">
         <v>3433</v>
@@ -2937,10 +2906,10 @@
         <v>123.759</v>
       </c>
       <c r="K50">
-        <v>0.14499999999999999</v>
+        <v>0.145</v>
       </c>
       <c r="L50">
-        <v>0.51700000000000002</v>
+        <v>0.517</v>
       </c>
       <c r="M50">
         <v>1.35</v>
@@ -2949,31 +2918,31 @@
         <v>772</v>
       </c>
       <c r="O50">
-        <v>123.83199999999999</v>
+        <v>123.832</v>
       </c>
       <c r="Q50">
         <v>0.22</v>
       </c>
       <c r="R50">
-        <v>0.51800000000000002</v>
+        <v>0.518</v>
       </c>
       <c r="T50">
         <v>8124</v>
       </c>
       <c r="U50">
-        <v>163.18799999999999</v>
+        <v>163.188</v>
       </c>
       <c r="W50">
-        <v>0.16500000000000001</v>
+        <v>0.165</v>
       </c>
       <c r="X50">
-        <v>0.92300000000000004</v>
+        <v>0.923</v>
       </c>
       <c r="Y50">
         <v>0.316</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="51">
       <c r="A51">
         <v>1999</v>
       </c>
@@ -2981,13 +2950,13 @@
         <v>11622</v>
       </c>
       <c r="C51">
-        <v>145.15700000000001</v>
+        <v>145.157</v>
       </c>
       <c r="E51">
-        <v>0.17499999999999999</v>
+        <v>0.175</v>
       </c>
       <c r="F51">
-        <v>0.77700000000000002</v>
+        <v>0.777</v>
       </c>
       <c r="G51">
         <v>0.318</v>
@@ -2996,13 +2965,13 @@
         <v>3364</v>
       </c>
       <c r="I51">
-        <v>121.95699999999999</v>
+        <v>121.957</v>
       </c>
       <c r="K51">
-        <v>0.17199999999999999</v>
+        <v>0.172</v>
       </c>
       <c r="L51">
-        <v>0.49099999999999999</v>
+        <v>0.491</v>
       </c>
       <c r="M51">
         <v>1.33</v>
@@ -3011,34 +2980,34 @@
         <v>776</v>
       </c>
       <c r="O51">
-        <v>125.21599999999999</v>
+        <v>125.216</v>
       </c>
       <c r="Q51">
-        <v>0.23400000000000001</v>
+        <v>0.234</v>
       </c>
       <c r="R51">
-        <v>0.58599999999999997</v>
+        <v>0.586</v>
       </c>
       <c r="S51">
-        <v>0.55900000000000005</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="T51">
         <v>7482</v>
       </c>
       <c r="U51">
-        <v>158.42500000000001</v>
+        <v>158.425</v>
       </c>
       <c r="W51">
-        <v>0.16400000000000001</v>
+        <v>0.164</v>
       </c>
       <c r="X51">
-        <v>0.92900000000000005</v>
+        <v>0.929</v>
       </c>
       <c r="Y51">
-        <v>0.34200000000000003</v>
-      </c>
-    </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.342</v>
+      </c>
+    </row>
+    <row r="52">
       <c r="A52">
         <v>2000</v>
       </c>
@@ -3046,16 +3015,16 @@
         <v>12051.367</v>
       </c>
       <c r="C52">
-        <v>146.51900000000001</v>
+        <v>146.519</v>
       </c>
       <c r="E52">
-        <v>0.17299999999999999</v>
+        <v>0.173</v>
       </c>
       <c r="F52">
-        <v>0.75900000000000001</v>
+        <v>0.759</v>
       </c>
       <c r="G52">
-        <v>0.29899999999999999</v>
+        <v>0.299</v>
       </c>
       <c r="H52">
         <v>3315.71</v>
@@ -3064,13 +3033,13 @@
         <v>122.986</v>
       </c>
       <c r="K52">
-        <v>0.17399999999999999</v>
+        <v>0.174</v>
       </c>
       <c r="L52">
         <v>0.498</v>
       </c>
       <c r="M52">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="N52">
         <v>731</v>
@@ -3088,54 +3057,54 @@
         <v>0.82</v>
       </c>
       <c r="T52">
-        <v>8004.6570000000002</v>
+        <v>8004.657</v>
       </c>
       <c r="U52">
-        <v>163.43600000000001</v>
+        <v>163.436</v>
       </c>
       <c r="W52">
-        <v>0.16800000000000001</v>
+        <v>0.168</v>
       </c>
       <c r="X52">
-        <v>0.92200000000000004</v>
+        <v>0.922</v>
       </c>
       <c r="Y52">
-        <v>0.38100000000000001</v>
-      </c>
-    </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.381</v>
+      </c>
+    </row>
+    <row r="53">
       <c r="A53">
         <v>2001</v>
       </c>
       <c r="B53">
-        <v>10577.852999999999</v>
+        <v>10577.853</v>
       </c>
       <c r="C53">
-        <v>145.21700000000001</v>
+        <v>145.217</v>
       </c>
       <c r="E53">
-        <v>0.19600000000000001</v>
+        <v>0.196</v>
       </c>
       <c r="F53">
-        <v>0.73899999999999999</v>
+        <v>0.739</v>
       </c>
       <c r="G53">
-        <v>0.28599999999999998</v>
+        <v>0.286</v>
       </c>
       <c r="H53">
         <v>2497.96</v>
       </c>
       <c r="I53">
-        <v>118.60899999999999</v>
+        <v>118.609</v>
       </c>
       <c r="K53">
-        <v>0.20699999999999999</v>
+        <v>0.207</v>
       </c>
       <c r="L53">
-        <v>0.48899999999999999</v>
+        <v>0.489</v>
       </c>
       <c r="M53">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="N53">
         <v>731</v>
@@ -3147,10 +3116,10 @@
         <v>0.215</v>
       </c>
       <c r="R53">
-        <v>0.54500000000000004</v>
+        <v>0.545</v>
       </c>
       <c r="S53">
-        <v>0.64200000000000002</v>
+        <v>0.642</v>
       </c>
       <c r="T53">
         <v>7348.893</v>
@@ -3162,30 +3131,30 @@
         <v>0.185</v>
       </c>
       <c r="X53">
-        <v>0.91200000000000003</v>
+        <v>0.912</v>
       </c>
       <c r="Y53">
         <v>0.39</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="54">
       <c r="A54">
         <v>2002</v>
       </c>
       <c r="B54">
-        <v>9973.1620000000003</v>
+        <v>9973.162</v>
       </c>
       <c r="C54">
-        <v>147.36500000000001</v>
+        <v>147.365</v>
       </c>
       <c r="E54">
-        <v>0.19400000000000001</v>
+        <v>0.194</v>
       </c>
       <c r="F54">
-        <v>0.75600000000000001</v>
+        <v>0.756</v>
       </c>
       <c r="G54">
-        <v>0.28299999999999997</v>
+        <v>0.283</v>
       </c>
       <c r="H54">
         <v>2598</v>
@@ -3194,13 +3163,13 @@
         <v>120.309</v>
       </c>
       <c r="K54">
-        <v>0.21099999999999999</v>
+        <v>0.211</v>
       </c>
       <c r="L54">
-        <v>0.47199999999999998</v>
+        <v>0.472</v>
       </c>
       <c r="M54">
-        <v>0.90400000000000003</v>
+        <v>0.904</v>
       </c>
       <c r="N54">
         <v>765</v>
@@ -3212,28 +3181,28 @@
         <v>0.224</v>
       </c>
       <c r="R54">
-        <v>0.51600000000000001</v>
+        <v>0.516</v>
       </c>
       <c r="S54">
-        <v>0.57599999999999996</v>
+        <v>0.576</v>
       </c>
       <c r="T54">
-        <v>6610.1620000000003</v>
+        <v>6610.162</v>
       </c>
       <c r="U54">
-        <v>163.11799999999999</v>
+        <v>163.118</v>
       </c>
       <c r="W54">
-        <v>0.18099999999999999</v>
+        <v>0.181</v>
       </c>
       <c r="X54">
-        <v>0.91800000000000004</v>
+        <v>0.918</v>
       </c>
       <c r="Y54">
-        <v>0.41099999999999998</v>
-      </c>
-    </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.411</v>
+      </c>
+    </row>
+    <row r="55">
       <c r="A55">
         <v>2003</v>
       </c>
@@ -3244,13 +3213,13 @@
         <v>143.404</v>
       </c>
       <c r="E55">
-        <v>0.17799999999999999</v>
+        <v>0.178</v>
       </c>
       <c r="F55">
         <v>0.755</v>
       </c>
       <c r="G55">
-        <v>0.28599999999999998</v>
+        <v>0.286</v>
       </c>
       <c r="H55">
         <v>2756.59</v>
@@ -3262,10 +3231,10 @@
         <v>0.191</v>
       </c>
       <c r="L55">
-        <v>0.46800000000000003</v>
+        <v>0.468</v>
       </c>
       <c r="M55">
-        <v>0.80200000000000005</v>
+        <v>0.802</v>
       </c>
       <c r="N55">
         <v>1032</v>
@@ -3274,31 +3243,31 @@
         <v>128.625</v>
       </c>
       <c r="Q55">
-        <v>0.24199999999999999</v>
+        <v>0.242</v>
       </c>
       <c r="R55">
-        <v>0.61699999999999999</v>
+        <v>0.617</v>
       </c>
       <c r="S55">
-        <v>0.78100000000000003</v>
+        <v>0.781</v>
       </c>
       <c r="T55">
         <v>7917.82</v>
       </c>
       <c r="U55">
-        <v>155.94200000000001</v>
+        <v>155.942</v>
       </c>
       <c r="W55">
         <v>0.16</v>
       </c>
       <c r="X55">
-        <v>0.89700000000000002</v>
+        <v>0.897</v>
       </c>
       <c r="Y55">
         <v>0.42</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="56">
       <c r="A56">
         <v>2004</v>
       </c>
@@ -3306,31 +3275,31 @@
         <v>12070.5</v>
       </c>
       <c r="C56">
-        <v>149.68899999999999</v>
+        <v>149.689</v>
       </c>
       <c r="E56">
-        <v>0.17299999999999999</v>
+        <v>0.173</v>
       </c>
       <c r="F56">
-        <v>0.79400000000000004</v>
+        <v>0.794</v>
       </c>
       <c r="G56">
-        <v>0.30199999999999999</v>
+        <v>0.302</v>
       </c>
       <c r="H56">
-        <v>2590.6799999999998</v>
+        <v>2590.68</v>
       </c>
       <c r="I56">
-        <v>121.72799999999999</v>
+        <v>121.728</v>
       </c>
       <c r="K56">
         <v>0.186</v>
       </c>
       <c r="L56">
-        <v>0.46800000000000003</v>
+        <v>0.468</v>
       </c>
       <c r="M56">
-        <v>0.82299999999999995</v>
+        <v>0.823</v>
       </c>
       <c r="N56">
         <v>1319</v>
@@ -3351,19 +3320,19 @@
         <v>8160.82</v>
       </c>
       <c r="U56">
-        <v>161.06899999999999</v>
+        <v>161.069</v>
       </c>
       <c r="W56">
         <v>0.16</v>
       </c>
       <c r="X56">
-        <v>0.91200000000000003</v>
+        <v>0.912</v>
       </c>
       <c r="Y56">
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.337</v>
+      </c>
+    </row>
+    <row r="57">
       <c r="A57">
         <v>2005</v>
       </c>
@@ -3374,13 +3343,13 @@
         <v>146.917</v>
       </c>
       <c r="E57">
-        <v>0.17799999999999999</v>
+        <v>0.178</v>
       </c>
       <c r="F57">
-        <v>0.75600000000000001</v>
+        <v>0.756</v>
       </c>
       <c r="G57">
-        <v>0.32300000000000001</v>
+        <v>0.323</v>
       </c>
       <c r="H57">
         <v>2272.86</v>
@@ -3392,7 +3361,7 @@
         <v>0.184</v>
       </c>
       <c r="L57">
-        <v>0.45500000000000002</v>
+        <v>0.455</v>
       </c>
       <c r="M57">
         <v>1.36</v>
@@ -3407,28 +3376,28 @@
         <v>0.249</v>
       </c>
       <c r="R57">
-        <v>0.61899999999999999</v>
+        <v>0.619</v>
       </c>
       <c r="S57">
         <v>1.038</v>
       </c>
       <c r="T57">
-        <v>9207.7360000000008</v>
+        <v>9207.736000000001</v>
       </c>
       <c r="U57">
-        <v>158.16900000000001</v>
+        <v>158.169</v>
       </c>
       <c r="W57">
-        <v>0.16500000000000001</v>
+        <v>0.165</v>
       </c>
       <c r="X57">
         <v>0.878</v>
       </c>
       <c r="Y57">
-        <v>0.27700000000000002</v>
-      </c>
-    </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.277</v>
+      </c>
+    </row>
+    <row r="58">
       <c r="A58">
         <v>2006</v>
       </c>
@@ -3442,10 +3411,10 @@
         <v>0.18</v>
       </c>
       <c r="F58">
-        <v>0.76100000000000001</v>
+        <v>0.761</v>
       </c>
       <c r="G58">
-        <v>0.33600000000000002</v>
+        <v>0.336</v>
       </c>
       <c r="H58">
         <v>1960.7</v>
@@ -3454,63 +3423,63 @@
         <v>120.761</v>
       </c>
       <c r="K58">
-        <v>0.19500000000000001</v>
+        <v>0.195</v>
       </c>
       <c r="L58">
-        <v>0.45700000000000002</v>
+        <v>0.457</v>
       </c>
       <c r="M58">
-        <v>1.0860000000000001</v>
+        <v>1.086</v>
       </c>
       <c r="N58">
         <v>949</v>
       </c>
       <c r="O58">
-        <v>131.06899999999999</v>
+        <v>131.069</v>
       </c>
       <c r="Q58">
-        <v>0.23200000000000001</v>
+        <v>0.232</v>
       </c>
       <c r="R58">
-        <v>0.63900000000000001</v>
+        <v>0.639</v>
       </c>
       <c r="S58">
-        <v>0.90600000000000003</v>
+        <v>0.906</v>
       </c>
       <c r="T58">
-        <v>8619.4410000000007</v>
+        <v>8619.441000000001</v>
       </c>
       <c r="U58">
         <v>158.791</v>
       </c>
       <c r="W58">
-        <v>0.16600000000000001</v>
+        <v>0.166</v>
       </c>
       <c r="X58">
-        <v>0.88200000000000001</v>
+        <v>0.882</v>
       </c>
       <c r="Y58">
-        <v>0.25900000000000001</v>
-      </c>
-    </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.259</v>
+      </c>
+    </row>
+    <row r="59">
       <c r="A59">
         <v>2007</v>
       </c>
       <c r="B59">
-        <v>12305.566000000001</v>
+        <v>12305.566</v>
       </c>
       <c r="C59">
         <v>145.196</v>
       </c>
       <c r="E59">
-        <v>0.18099999999999999</v>
+        <v>0.181</v>
       </c>
       <c r="F59">
-        <v>0.74199999999999999</v>
+        <v>0.742</v>
       </c>
       <c r="G59">
-        <v>0.34200000000000003</v>
+        <v>0.342</v>
       </c>
       <c r="H59">
         <v>2473.9</v>
@@ -3519,10 +3488,10 @@
         <v>117.621</v>
       </c>
       <c r="K59">
-        <v>0.20499999999999999</v>
+        <v>0.205</v>
       </c>
       <c r="L59">
-        <v>0.44900000000000001</v>
+        <v>0.449</v>
       </c>
       <c r="M59">
         <v>1.36</v>
@@ -3540,42 +3509,42 @@
         <v>0.6</v>
       </c>
       <c r="S59">
-        <v>1.0389999999999999</v>
+        <v>1.039</v>
       </c>
       <c r="T59">
-        <v>9053.6659999999993</v>
+        <v>9053.665999999999</v>
       </c>
       <c r="U59">
         <v>157.15</v>
       </c>
       <c r="W59">
-        <v>0.16600000000000001</v>
+        <v>0.166</v>
       </c>
       <c r="X59">
-        <v>0.86399999999999999</v>
+        <v>0.864</v>
       </c>
       <c r="Y59">
-        <v>0.33100000000000002</v>
-      </c>
-    </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.331</v>
+      </c>
+    </row>
+    <row r="60">
       <c r="A60">
         <v>2008</v>
       </c>
       <c r="B60">
-        <v>11102.888000000001</v>
+        <v>11102.888</v>
       </c>
       <c r="C60">
         <v>147.315</v>
       </c>
       <c r="E60">
-        <v>0.17899999999999999</v>
+        <v>0.179</v>
       </c>
       <c r="F60">
-        <v>0.77600000000000002</v>
+        <v>0.776</v>
       </c>
       <c r="G60">
-        <v>0.33800000000000002</v>
+        <v>0.338</v>
       </c>
       <c r="H60">
         <v>2404.66</v>
@@ -3584,10 +3553,10 @@
         <v>118.889</v>
       </c>
       <c r="K60">
-        <v>0.20499999999999999</v>
+        <v>0.205</v>
       </c>
       <c r="L60">
-        <v>0.45500000000000002</v>
+        <v>0.455</v>
       </c>
       <c r="M60">
         <v>1.228</v>
@@ -3596,39 +3565,39 @@
         <v>747</v>
       </c>
       <c r="O60">
-        <v>131.15600000000001</v>
+        <v>131.156</v>
       </c>
       <c r="Q60">
         <v>0.22</v>
       </c>
       <c r="R60">
-        <v>0.64900000000000002</v>
+        <v>0.649</v>
       </c>
       <c r="S60">
         <v>1.002</v>
       </c>
       <c r="T60">
-        <v>7951.2280000000001</v>
+        <v>7951.228</v>
       </c>
       <c r="U60">
         <v>159.483</v>
       </c>
       <c r="W60">
-        <v>0.16300000000000001</v>
+        <v>0.163</v>
       </c>
       <c r="X60">
-        <v>0.90400000000000003</v>
+        <v>0.904</v>
       </c>
       <c r="Y60">
         <v>0.377</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="61">
       <c r="A61">
         <v>2009</v>
       </c>
       <c r="B61">
-        <v>12146.906999999999</v>
+        <v>12146.907</v>
       </c>
       <c r="C61">
         <v>152.369</v>
@@ -3637,10 +3606,10 @@
         <v>0.183</v>
       </c>
       <c r="F61">
-        <v>0.80500000000000005</v>
+        <v>0.805</v>
       </c>
       <c r="G61">
-        <v>0.33700000000000002</v>
+        <v>0.337</v>
       </c>
       <c r="H61">
         <v>2691.31</v>
@@ -3649,10 +3618,10 @@
         <v>123.735</v>
       </c>
       <c r="K61">
-        <v>0.21099999999999999</v>
+        <v>0.211</v>
       </c>
       <c r="L61">
-        <v>0.48899999999999999</v>
+        <v>0.489</v>
       </c>
       <c r="M61">
         <v>1.056</v>
@@ -3661,34 +3630,34 @@
         <v>898</v>
       </c>
       <c r="O61">
-        <v>130.84800000000001</v>
+        <v>130.848</v>
       </c>
       <c r="Q61">
-        <v>0.20699999999999999</v>
+        <v>0.207</v>
       </c>
       <c r="R61">
-        <v>0.67100000000000004</v>
+        <v>0.671</v>
       </c>
       <c r="S61">
-        <v>1.1240000000000001</v>
+        <v>1.124</v>
       </c>
       <c r="T61">
-        <v>8557.5969999999998</v>
+        <v>8557.597</v>
       </c>
       <c r="U61">
-        <v>168.12700000000001</v>
+        <v>168.127</v>
       </c>
       <c r="W61">
-        <v>0.16600000000000001</v>
+        <v>0.166</v>
       </c>
       <c r="X61">
-        <v>0.95799999999999996</v>
+        <v>0.958</v>
       </c>
       <c r="Y61">
-        <v>0.39800000000000002</v>
-      </c>
-    </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.398</v>
+      </c>
+    </row>
+    <row r="62">
       <c r="A62">
         <v>2010</v>
       </c>
@@ -3702,10 +3671,10 @@
         <v>0.182</v>
       </c>
       <c r="F62">
-        <v>0.79200000000000004</v>
+        <v>0.792</v>
       </c>
       <c r="G62">
-        <v>0.33300000000000002</v>
+        <v>0.333</v>
       </c>
       <c r="H62">
         <v>2204.29</v>
@@ -3714,46 +3683,46 @@
         <v>127.46</v>
       </c>
       <c r="K62">
-        <v>0.19600000000000001</v>
+        <v>0.196</v>
       </c>
       <c r="L62">
         <v>0.505</v>
       </c>
       <c r="M62">
-        <v>0.76200000000000001</v>
+        <v>0.762</v>
       </c>
       <c r="N62">
         <v>1054</v>
       </c>
       <c r="O62">
-        <v>130.45500000000001</v>
+        <v>130.455</v>
       </c>
       <c r="Q62">
         <v>0.218</v>
       </c>
       <c r="R62">
-        <v>0.63800000000000001</v>
+        <v>0.638</v>
       </c>
       <c r="S62">
-        <v>0.98099999999999998</v>
+        <v>0.981</v>
       </c>
       <c r="T62">
-        <v>8413.8799999999992</v>
+        <v>8413.879999999999</v>
       </c>
       <c r="U62">
-        <v>167.66900000000001</v>
+        <v>167.669</v>
       </c>
       <c r="W62">
-        <v>0.16900000000000001</v>
+        <v>0.169</v>
       </c>
       <c r="X62">
-        <v>0.93799999999999994</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="Y62">
-        <v>0.41399999999999998</v>
-      </c>
-    </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.414</v>
+      </c>
+    </row>
+    <row r="63">
       <c r="A63">
         <v>2011</v>
       </c>
@@ -3764,13 +3733,13 @@
         <v>151.4</v>
       </c>
       <c r="E63">
-        <v>0.17499999999999999</v>
+        <v>0.175</v>
       </c>
       <c r="F63">
         <v>0.748</v>
       </c>
       <c r="G63">
-        <v>0.34200000000000003</v>
+        <v>0.342</v>
       </c>
       <c r="H63">
         <v>2571.5</v>
@@ -3782,7 +3751,7 @@
         <v>0.185</v>
       </c>
       <c r="L63">
-        <v>0.45700000000000002</v>
+        <v>0.457</v>
       </c>
       <c r="M63">
         <v>1.056</v>
@@ -3791,7 +3760,7 @@
         <v>1202</v>
       </c>
       <c r="O63">
-        <v>131.39400000000001</v>
+        <v>131.394</v>
       </c>
       <c r="Q63">
         <v>0.222</v>
@@ -3812,18 +3781,18 @@
         <v>0.158</v>
       </c>
       <c r="X63">
-        <v>0.92500000000000004</v>
+        <v>0.925</v>
       </c>
       <c r="Y63">
-        <v>0.40500000000000003</v>
-      </c>
-    </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.405</v>
+      </c>
+    </row>
+    <row r="64">
       <c r="A64">
         <v>2012</v>
       </c>
       <c r="B64">
-        <v>13917.041999999999</v>
+        <v>13917.042</v>
       </c>
       <c r="C64">
         <v>150.773</v>
@@ -3832,10 +3801,10 @@
         <v>0.186</v>
       </c>
       <c r="F64">
-        <v>0.76600000000000001</v>
+        <v>0.766</v>
       </c>
       <c r="G64">
-        <v>0.35599999999999998</v>
+        <v>0.356</v>
       </c>
       <c r="H64">
         <v>3346.69</v>
@@ -3847,16 +3816,16 @@
         <v>0.218</v>
       </c>
       <c r="L64">
-        <v>0.45400000000000001</v>
+        <v>0.454</v>
       </c>
       <c r="M64">
-        <v>1.0660000000000001</v>
+        <v>1.066</v>
       </c>
       <c r="N64">
         <v>882</v>
       </c>
       <c r="O64">
-        <v>135.41800000000001</v>
+        <v>135.418</v>
       </c>
       <c r="Q64">
         <v>0.217</v>
@@ -3868,22 +3837,22 @@
         <v>1.079</v>
       </c>
       <c r="T64">
-        <v>9688.3520000000008</v>
+        <v>9688.352000000001</v>
       </c>
       <c r="U64">
-        <v>167.87100000000001</v>
+        <v>167.871</v>
       </c>
       <c r="W64">
-        <v>0.16300000000000001</v>
+        <v>0.163</v>
       </c>
       <c r="X64">
-        <v>0.93700000000000006</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="Y64">
-        <v>0.44800000000000001</v>
-      </c>
-    </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.448</v>
+      </c>
+    </row>
+    <row r="65">
       <c r="A65">
         <v>2013</v>
       </c>
@@ -3891,13 +3860,13 @@
         <v>12078.364</v>
       </c>
       <c r="C65">
-        <v>149.22900000000001</v>
+        <v>149.229</v>
       </c>
       <c r="E65">
-        <v>0.19500000000000001</v>
+        <v>0.195</v>
       </c>
       <c r="F65">
-        <v>0.80300000000000005</v>
+        <v>0.803</v>
       </c>
       <c r="G65">
         <v>0.378</v>
@@ -3906,7 +3875,7 @@
         <v>2812.13</v>
       </c>
       <c r="I65">
-        <v>122.01600000000001</v>
+        <v>122.016</v>
       </c>
       <c r="K65">
         <v>0.253</v>
@@ -3915,84 +3884,84 @@
         <v>0.48</v>
       </c>
       <c r="M65">
-        <v>0.93400000000000005</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="N65">
         <v>1438</v>
       </c>
       <c r="O65">
-        <v>148.96899999999999</v>
+        <v>148.969</v>
       </c>
       <c r="Q65">
-        <v>0.23300000000000001</v>
+        <v>0.233</v>
       </c>
       <c r="R65">
-        <v>0.83299999999999996</v>
+        <v>0.833</v>
       </c>
       <c r="S65">
-        <v>1.1399999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="T65">
-        <v>7828.2340000000004</v>
+        <v>7828.234</v>
       </c>
       <c r="U65">
         <v>160.166</v>
       </c>
       <c r="W65">
-        <v>0.16400000000000001</v>
+        <v>0.164</v>
       </c>
       <c r="X65">
-        <v>0.92500000000000004</v>
+        <v>0.925</v>
       </c>
       <c r="Y65">
-        <v>0.29699999999999999</v>
-      </c>
-    </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.297</v>
+      </c>
+    </row>
+    <row r="66">
       <c r="A66">
         <v>2014</v>
       </c>
       <c r="B66">
-        <v>10714.852000000001</v>
+        <v>10714.852</v>
       </c>
       <c r="C66">
         <v>151.488</v>
       </c>
       <c r="E66">
-        <v>0.18099999999999999</v>
+        <v>0.181</v>
       </c>
       <c r="F66">
-        <v>0.79200000000000004</v>
+        <v>0.792</v>
       </c>
       <c r="G66">
-        <v>0.39400000000000002</v>
+        <v>0.394</v>
       </c>
       <c r="H66">
         <v>1816.16</v>
       </c>
       <c r="I66">
-        <v>120.44199999999999</v>
+        <v>120.442</v>
       </c>
       <c r="K66">
-        <v>0.20499999999999999</v>
+        <v>0.205</v>
       </c>
       <c r="L66">
         <v>0.43</v>
       </c>
       <c r="M66">
-        <v>0.74099999999999999</v>
+        <v>0.741</v>
       </c>
       <c r="N66">
         <v>1241</v>
       </c>
       <c r="O66">
-        <v>142.26300000000001</v>
+        <v>142.263</v>
       </c>
       <c r="Q66">
         <v>0.216</v>
       </c>
       <c r="R66">
-        <v>0.78300000000000003</v>
+        <v>0.783</v>
       </c>
       <c r="S66">
         <v>0.996</v>
@@ -4004,16 +3973,16 @@
         <v>165.751</v>
       </c>
       <c r="W66">
-        <v>0.16400000000000001</v>
+        <v>0.164</v>
       </c>
       <c r="X66">
-        <v>0.93899999999999995</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="Y66">
         <v>0.35</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="67">
       <c r="A67">
         <v>2015</v>
       </c>
@@ -4030,7 +3999,7 @@
         <v>0.8</v>
       </c>
       <c r="G67">
-        <v>0.39700000000000002</v>
+        <v>0.397</v>
       </c>
       <c r="H67">
         <v>1592.8</v>
@@ -4042,16 +4011,16 @@
         <v>0.216</v>
       </c>
       <c r="L67">
-        <v>0.40799999999999997</v>
+        <v>0.408</v>
       </c>
       <c r="M67">
-        <v>0.76200000000000001</v>
+        <v>0.762</v>
       </c>
       <c r="N67">
         <v>1420</v>
       </c>
       <c r="O67">
-        <v>158.99100000000001</v>
+        <v>158.991</v>
       </c>
       <c r="Q67">
         <v>0.214</v>
@@ -4060,25 +4029,25 @@
         <v>0.875</v>
       </c>
       <c r="S67">
-        <v>0.99199999999999999</v>
+        <v>0.992</v>
       </c>
       <c r="T67">
         <v>7757.424</v>
       </c>
       <c r="U67">
-        <v>168.19900000000001</v>
+        <v>168.199</v>
       </c>
       <c r="W67">
-        <v>0.17199999999999999</v>
+        <v>0.172</v>
       </c>
       <c r="X67">
-        <v>0.94199999999999995</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="Y67">
-        <v>0.33400000000000002</v>
-      </c>
-    </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.334</v>
+      </c>
+    </row>
+    <row r="68">
       <c r="A68">
         <v>2016</v>
       </c>
@@ -4086,16 +4055,16 @@
         <v>10505.394</v>
       </c>
       <c r="C68">
-        <v>155.99199999999999</v>
+        <v>155.992</v>
       </c>
       <c r="E68">
         <v>0.189</v>
       </c>
       <c r="F68">
-        <v>0.81299999999999994</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G68">
-        <v>0.40200000000000002</v>
+        <v>0.402</v>
       </c>
       <c r="H68">
         <v>1388.6</v>
@@ -4107,43 +4076,43 @@
         <v>0.224</v>
       </c>
       <c r="L68">
-        <v>0.42899999999999999</v>
+        <v>0.429</v>
       </c>
       <c r="M68">
-        <v>0.77200000000000002</v>
+        <v>0.772</v>
       </c>
       <c r="N68">
         <v>1459</v>
       </c>
       <c r="O68">
-        <v>155.16300000000001</v>
+        <v>155.163</v>
       </c>
       <c r="Q68">
-        <v>0.23200000000000001</v>
+        <v>0.232</v>
       </c>
       <c r="R68">
-        <v>0.84699999999999998</v>
+        <v>0.847</v>
       </c>
       <c r="S68">
-        <v>1.1020000000000001</v>
+        <v>1.102</v>
       </c>
       <c r="T68">
-        <v>7657.7939999999999</v>
+        <v>7657.794</v>
       </c>
       <c r="U68">
-        <v>170.85499999999999</v>
+        <v>170.855</v>
       </c>
       <c r="W68">
-        <v>0.16700000000000001</v>
+        <v>0.167</v>
       </c>
       <c r="X68">
         <v>0.96</v>
       </c>
       <c r="Y68">
-        <v>1.9E-2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.019</v>
+      </c>
+    </row>
+    <row r="69">
       <c r="A69">
         <v>2017</v>
       </c>
@@ -4154,10 +4123,10 @@
         <v>157.958</v>
       </c>
       <c r="E69">
-        <v>0.19900000000000001</v>
+        <v>0.199</v>
       </c>
       <c r="F69">
-        <v>0.79800000000000004</v>
+        <v>0.798</v>
       </c>
       <c r="G69">
         <v>0.41</v>
@@ -4169,28 +4138,28 @@
         <v>118.267</v>
       </c>
       <c r="K69">
-        <v>0.23300000000000001</v>
+        <v>0.233</v>
       </c>
       <c r="L69">
-        <v>0.42199999999999999</v>
+        <v>0.422</v>
       </c>
       <c r="M69">
-        <v>0.80200000000000005</v>
+        <v>0.802</v>
       </c>
       <c r="N69">
         <v>1871</v>
       </c>
       <c r="O69">
-        <v>153.28399999999999</v>
+        <v>153.284</v>
       </c>
       <c r="Q69">
-        <v>0.23499999999999999</v>
+        <v>0.235</v>
       </c>
       <c r="R69">
-        <v>0.83099999999999996</v>
+        <v>0.831</v>
       </c>
       <c r="S69">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="T69">
         <v>7139.98</v>
@@ -4199,21 +4168,21 @@
         <v>174.77</v>
       </c>
       <c r="W69">
-        <v>0.17799999999999999</v>
+        <v>0.178</v>
       </c>
       <c r="X69">
-        <v>0.94199999999999995</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="Y69">
-        <v>1.9E-2</v>
-      </c>
-    </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.019</v>
+      </c>
+    </row>
+    <row r="70">
       <c r="A70">
         <v>2018</v>
       </c>
       <c r="B70">
-        <v>9032.7819999999992</v>
+        <v>9032.781999999999</v>
       </c>
       <c r="C70">
         <v>151.703</v>
@@ -4222,58 +4191,58 @@
         <v>0.187</v>
       </c>
       <c r="F70">
-        <v>0.76700000000000002</v>
+        <v>0.767</v>
       </c>
       <c r="G70">
-        <v>0.41599999999999998</v>
+        <v>0.416</v>
       </c>
       <c r="H70">
         <v>1105.72</v>
       </c>
       <c r="I70">
-        <v>115.56399999999999</v>
+        <v>115.564</v>
       </c>
       <c r="K70">
-        <v>0.19400000000000001</v>
+        <v>0.194</v>
       </c>
       <c r="L70">
-        <v>0.35599999999999998</v>
+        <v>0.356</v>
       </c>
       <c r="M70">
-        <v>0.97499999999999998</v>
+        <v>0.975</v>
       </c>
       <c r="N70">
         <v>1670</v>
       </c>
       <c r="O70">
-        <v>145.95099999999999</v>
+        <v>145.951</v>
       </c>
       <c r="Q70">
         <v>0.219</v>
       </c>
       <c r="R70">
-        <v>0.82699999999999996</v>
+        <v>0.827</v>
       </c>
       <c r="S70">
-        <v>1.1040000000000001</v>
+        <v>1.104</v>
       </c>
       <c r="T70">
-        <v>6257.0619999999999</v>
+        <v>6257.062</v>
       </c>
       <c r="U70">
         <v>167.309</v>
       </c>
       <c r="W70">
-        <v>0.17799999999999999</v>
+        <v>0.178</v>
       </c>
       <c r="X70">
-        <v>0.91900000000000004</v>
+        <v>0.919</v>
       </c>
       <c r="Y70">
-        <v>1.7999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.018</v>
+      </c>
+    </row>
+    <row r="71">
       <c r="A71">
         <v>2019</v>
       </c>
@@ -4281,28 +4250,28 @@
         <v>10257.431</v>
       </c>
       <c r="C71">
-        <v>152.20699999999999</v>
+        <v>152.207</v>
       </c>
       <c r="E71">
-        <v>0.17699999999999999</v>
+        <v>0.177</v>
       </c>
       <c r="F71">
-        <v>0.80100000000000005</v>
+        <v>0.801</v>
       </c>
       <c r="G71">
-        <v>0.41599999999999998</v>
+        <v>0.416</v>
       </c>
       <c r="H71">
         <v>1455.95</v>
       </c>
       <c r="I71">
-        <v>120.36799999999999</v>
+        <v>120.368</v>
       </c>
       <c r="K71">
         <v>0.193</v>
       </c>
       <c r="L71">
-        <v>0.40600000000000003</v>
+        <v>0.406</v>
       </c>
       <c r="M71">
         <v>1.147</v>
@@ -4314,7 +4283,7 @@
         <v>148.749</v>
       </c>
       <c r="Q71">
-        <v>0.20300000000000001</v>
+        <v>0.203</v>
       </c>
       <c r="R71">
         <v>0.879</v>
@@ -4323,22 +4292,22 @@
         <v>1.482</v>
       </c>
       <c r="T71">
-        <v>6455.4809999999998</v>
+        <v>6455.481</v>
       </c>
       <c r="U71">
-        <v>165.63499999999999</v>
+        <v>165.635</v>
       </c>
       <c r="W71">
-        <v>0.16500000000000001</v>
+        <v>0.165</v>
       </c>
       <c r="X71">
-        <v>0.94299999999999995</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="Y71">
-        <v>2.3E-2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.023</v>
+      </c>
+    </row>
+    <row r="72">
       <c r="A72">
         <v>2020</v>
       </c>
@@ -4349,13 +4318,13 @@
         <v>150.922</v>
       </c>
       <c r="E72">
-        <v>0.17299999999999999</v>
+        <v>0.173</v>
       </c>
       <c r="F72">
-        <v>0.79300000000000004</v>
+        <v>0.793</v>
       </c>
       <c r="G72">
-        <v>0.41199999999999998</v>
+        <v>0.412</v>
       </c>
       <c r="H72">
         <v>1150.04</v>
@@ -4376,31 +4345,31 @@
         <v>2044</v>
       </c>
       <c r="O72">
-        <v>145.96700000000001</v>
+        <v>145.967</v>
       </c>
       <c r="Q72">
-        <v>0.20399999999999999</v>
+        <v>0.204</v>
       </c>
       <c r="R72">
-        <v>0.81599999999999995</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="S72">
         <v>1.44</v>
       </c>
       <c r="T72">
-        <v>7302.2550000000001</v>
+        <v>7302.255</v>
       </c>
       <c r="U72">
-        <v>163.62100000000001</v>
+        <v>163.621</v>
       </c>
       <c r="W72">
-        <v>0.16300000000000001</v>
+        <v>0.163</v>
       </c>
       <c r="X72">
-        <v>0.92800000000000005</v>
+        <v>0.928</v>
       </c>
       <c r="Y72">
-        <v>2.1999999999999999E-2</v>
+        <v>0.022</v>
       </c>
     </row>
   </sheetData>

--- a/Indicator_4/Real_data/Swordfish_NAtl.xlsx
+++ b/Indicator_4/Real_data/Swordfish_NAtl.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
     <sheet name="Time_series" sheetId="2" r:id="rId2"/>
+    <sheet name="B_BMSY" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>312.27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -498,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>312.27</t>
+          <t>0.373</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4375,4 +4376,954 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C72"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>StDev</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SSB_1950</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>5.094169606822854</v>
+      </c>
+      <c r="C2">
+        <v>0.0667000871470755</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SSB_1951</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>5.019248504539263</v>
+      </c>
+      <c r="C3">
+        <v>0.06703598412738702</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SSB_1952</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>4.967721738541852</v>
+      </c>
+      <c r="C4">
+        <v>0.06712863077560897</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SSB_1953</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>4.908453266323154</v>
+      </c>
+      <c r="C5">
+        <v>0.06713793774483674</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SSB_1954</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>4.84770413990913</v>
+      </c>
+      <c r="C6">
+        <v>0.06711340118959988</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SSB_1955</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>4.789366364613211</v>
+      </c>
+      <c r="C7">
+        <v>0.06686930476939869</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SSB_1956</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>4.730690154072645</v>
+      </c>
+      <c r="C8">
+        <v>0.06670897107224746</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SSB_1957</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>4.680897868704046</v>
+      </c>
+      <c r="C9">
+        <v>0.06652663908419422</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SSB_1958</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>4.616510563410073</v>
+      </c>
+      <c r="C10">
+        <v>0.06651733211496645</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SSB_1959</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>4.54945808056451</v>
+      </c>
+      <c r="C11">
+        <v>0.06646995118071596</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SSB_1960</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>4.462734049123876</v>
+      </c>
+      <c r="C12">
+        <v>0.06648348859050181</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SSB_1961</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>4.435490011929843</v>
+      </c>
+      <c r="C13">
+        <v>0.06633584621502484</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SSB_1962</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>4.40833058354697</v>
+      </c>
+      <c r="C14">
+        <v>0.0663603827702617</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SSB_1963</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>4.367337614539178</v>
+      </c>
+      <c r="C15">
+        <v>0.06647502770938565</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SSB_1964</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>4.222237733837602</v>
+      </c>
+      <c r="C16">
+        <v>0.06663070792192298</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SSB_1965</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>4.068744659068796</v>
+      </c>
+      <c r="C17">
+        <v>0.06679231075124163</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SSB_1966</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>3.968745505156907</v>
+      </c>
+      <c r="C18">
+        <v>0.06651521689468741</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SSB_1967</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>3.86565812963762</v>
+      </c>
+      <c r="C19">
+        <v>0.06636799756326624</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SSB_1968</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>3.76989364672437</v>
+      </c>
+      <c r="C20">
+        <v>0.06609809545566075</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SSB_1969</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>3.683228841451549</v>
+      </c>
+      <c r="C21">
+        <v>0.06587599732636157</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SSB_1970</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>3.602473961638365</v>
+      </c>
+      <c r="C22">
+        <v>0.06558663519218891</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SSB_1971</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>3.517420954218172</v>
+      </c>
+      <c r="C23">
+        <v>0.06521308729091048</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SSB_1972</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>3.529604623025442</v>
+      </c>
+      <c r="C24">
+        <v>0.06476466059175402</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SSB_1973</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>3.553130102968924</v>
+      </c>
+      <c r="C25">
+        <v>0.06439788139536851</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SSB_1974</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>3.562149402238749</v>
+      </c>
+      <c r="C26">
+        <v>0.06427350644296097</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SSB_1975</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>3.563524295420125</v>
+      </c>
+      <c r="C27">
+        <v>0.06407129138428476</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SSB_1976</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>3.522104051915966</v>
+      </c>
+      <c r="C28">
+        <v>0.06406959920806153</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SSB_1977</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>3.511324889373979</v>
+      </c>
+      <c r="C29">
+        <v>0.06388557504378506</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SSB_1978</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>3.505647638145036</v>
+      </c>
+      <c r="C30">
+        <v>0.06378827491094922</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SSB_1979</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>3.401629565702972</v>
+      </c>
+      <c r="C31">
+        <v>0.06392237987664035</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SSB_1980</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>3.290838557927422</v>
+      </c>
+      <c r="C32">
+        <v>0.06389530505706864</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SSB_1981</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>3.15826501171832</v>
+      </c>
+      <c r="C33">
+        <v>0.06425996903317512</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SSB_1982</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>3.053747747290403</v>
+      </c>
+      <c r="C34">
+        <v>0.06473293228756843</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SSB_1983</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>2.897758712592329</v>
+      </c>
+      <c r="C35">
+        <v>0.06624658391924935</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SSB_1984</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>2.688487279065242</v>
+      </c>
+      <c r="C36">
+        <v>0.06962416766082019</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SSB_1985</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>2.493747408855158</v>
+      </c>
+      <c r="C37">
+        <v>0.07317519946527232</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SSB_1986</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>2.282635733685306</v>
+      </c>
+      <c r="C38">
+        <v>0.07558697362743357</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SSB_1987</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>2.041559848042575</v>
+      </c>
+      <c r="C39">
+        <v>0.07668815730470172</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SSB_1988</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>1.8149901430735</v>
+      </c>
+      <c r="C40">
+        <v>0.07693775329762842</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SSB_1989</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>1.627623930756149</v>
+      </c>
+      <c r="C41">
+        <v>0.07607432037972434</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SSB_1990</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>1.47995194219526</v>
+      </c>
+      <c r="C42">
+        <v>0.07427384487820561</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SSB_1991</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>1.379144774136779</v>
+      </c>
+      <c r="C43">
+        <v>0.07261678131160579</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SSB_1992</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>1.307536106810163</v>
+      </c>
+      <c r="C44">
+        <v>0.07148852281476592</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SSB_1993</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>1.236071274462522</v>
+      </c>
+      <c r="C45">
+        <v>0.07057897809477878</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SSB_1994</t>
+        </is>
+      </c>
+      <c r="B46">
+        <v>1.127277034630386</v>
+      </c>
+      <c r="C46">
+        <v>0.06937330253572606</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SSB_1995</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>1.036868289463665</v>
+      </c>
+      <c r="C47">
+        <v>0.06776911947610224</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SSB_1996</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>0.930540396476889</v>
+      </c>
+      <c r="C48">
+        <v>0.06568731967747121</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SSB_1997</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>0.8486009933074431</v>
+      </c>
+      <c r="C49">
+        <v>0.06386907632560855</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SSB_1998</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>0.7975480366525369</v>
+      </c>
+      <c r="C50">
+        <v>0.06249037574773037</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SSB_1999</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>0.7616992833633695</v>
+      </c>
+      <c r="C51">
+        <v>0.06119332267262313</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SSB_2000</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>0.7543806211978915</v>
+      </c>
+      <c r="C52">
+        <v>0.06045341861901498</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SSB_2001</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>0.7633829987054852</v>
+      </c>
+      <c r="C53">
+        <v>0.06066959413153285</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SSB_2002</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>0.8041390630420252</v>
+      </c>
+      <c r="C54">
+        <v>0.06229789070233774</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SSB_2003</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>0.862345694680644</v>
+      </c>
+      <c r="C55">
+        <v>0.06475323840224721</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SSB_2004</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>0.8959269318306807</v>
+      </c>
+      <c r="C56">
+        <v>0.06711340118959988</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SSB_2005</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>0.9112665092942779</v>
+      </c>
+      <c r="C57">
+        <v>0.06925654237632306</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SSB_2006</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>0.9025137277796109</v>
+      </c>
+      <c r="C58">
+        <v>0.07071096784019087</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SSB_2007</t>
+        </is>
+      </c>
+      <c r="B59">
+        <v>0.8977671734734455</v>
+      </c>
+      <c r="C59">
+        <v>0.07169243004966537</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SSB_2008</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>0.888984778874872</v>
+      </c>
+      <c r="C60">
+        <v>0.07195133301181984</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SSB_2009</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>0.9117022446717601</v>
+      </c>
+      <c r="C61">
+        <v>0.07252244248716061</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SSB_2010</t>
+        </is>
+      </c>
+      <c r="B62">
+        <v>0.9502711712397729</v>
+      </c>
+      <c r="C62">
+        <v>0.0738436090734489</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SSB_2011</t>
+        </is>
+      </c>
+      <c r="B63">
+        <v>1.007043683529203</v>
+      </c>
+      <c r="C63">
+        <v>0.07637002817473411</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SSB_2012</t>
+        </is>
+      </c>
+      <c r="B64">
+        <v>1.051201022074439</v>
+      </c>
+      <c r="C64">
+        <v>0.07910246973119781</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SSB_2013</t>
+        </is>
+      </c>
+      <c r="B65">
+        <v>1.058980802260747</v>
+      </c>
+      <c r="C65">
+        <v>0.08100574493827786</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SSB_2014</t>
+        </is>
+      </c>
+      <c r="B66">
+        <v>1.071185623270807</v>
+      </c>
+      <c r="C66">
+        <v>0.08248470695738254</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SSB_2015</t>
+        </is>
+      </c>
+      <c r="B67">
+        <v>1.093594266906956</v>
+      </c>
+      <c r="C67">
+        <v>0.08408212131211344</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SSB_2016</t>
+        </is>
+      </c>
+      <c r="B68">
+        <v>1.108570026482558</v>
+      </c>
+      <c r="C68">
+        <v>0.08573495443815518</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SSB_2017</t>
+        </is>
+      </c>
+      <c r="B69">
+        <v>1.108616561328697</v>
+      </c>
+      <c r="C69">
+        <v>0.08710604022302883</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SSB_2018</t>
+        </is>
+      </c>
+      <c r="B70">
+        <v>1.09805738169573</v>
+      </c>
+      <c r="C70">
+        <v>0.08811753856046568</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SSB_2019</t>
+        </is>
+      </c>
+      <c r="B71">
+        <v>1.106281358140637</v>
+      </c>
+      <c r="C71">
+        <v>0.08900635412171823</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SSB_2020</t>
+        </is>
+      </c>
+      <c r="B72">
+        <v>1.106793241448164</v>
+      </c>
+      <c r="C72">
+        <v>0.08991801406198441</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>